--- a/static/investmentSchedule_results.xlsx
+++ b/static/investmentSchedule_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,1442 +450,7202 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96802</v>
+        <v>12540</v>
       </c>
       <c r="B2" t="n">
-        <v>96802</v>
+        <v>12540</v>
       </c>
       <c r="C2" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>3596802</v>
+        <v>12540</v>
       </c>
       <c r="F2" t="n">
-        <v>3596802</v>
+        <v>12540</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>193604</v>
+        <v>25080</v>
       </c>
       <c r="B3" t="n">
-        <v>194450</v>
+        <v>25170</v>
       </c>
       <c r="C3" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3530571</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3693604</v>
+        <v>25080</v>
       </c>
       <c r="F3" t="n">
-        <v>3725021</v>
+        <v>25170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>290406</v>
+        <v>37620</v>
       </c>
       <c r="B4" t="n">
-        <v>292950</v>
+        <v>37891</v>
       </c>
       <c r="C4" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3561409</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3790406</v>
+        <v>37620</v>
       </c>
       <c r="F4" t="n">
-        <v>3854359</v>
+        <v>37891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>387208</v>
+        <v>50160</v>
       </c>
       <c r="B5" t="n">
-        <v>392311</v>
+        <v>50704</v>
       </c>
       <c r="C5" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3592516</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3887208</v>
+        <v>50160</v>
       </c>
       <c r="F5" t="n">
-        <v>3984827</v>
+        <v>50704</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>484010</v>
+        <v>62700</v>
       </c>
       <c r="B6" t="n">
-        <v>492540</v>
+        <v>63609</v>
       </c>
       <c r="C6" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3623895</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3984010</v>
+        <v>62700</v>
       </c>
       <c r="F6" t="n">
-        <v>4116435</v>
+        <v>63609</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>580812</v>
+        <v>75240</v>
       </c>
       <c r="B7" t="n">
-        <v>593644</v>
+        <v>76607</v>
       </c>
       <c r="C7" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3655548</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>4080812</v>
+        <v>75240</v>
       </c>
       <c r="F7" t="n">
-        <v>4249192</v>
+        <v>76607</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>677614</v>
+        <v>87780</v>
       </c>
       <c r="B8" t="n">
-        <v>695631</v>
+        <v>89699</v>
       </c>
       <c r="C8" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>3687477</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4177614</v>
+        <v>87780</v>
       </c>
       <c r="F8" t="n">
-        <v>4383108</v>
+        <v>89699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>774416</v>
+        <v>100320</v>
       </c>
       <c r="B9" t="n">
-        <v>798509</v>
+        <v>102885</v>
       </c>
       <c r="C9" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3719685</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>4274416</v>
+        <v>100320</v>
       </c>
       <c r="F9" t="n">
-        <v>4518194</v>
+        <v>102885</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>871218</v>
+        <v>112860</v>
       </c>
       <c r="B10" t="n">
-        <v>902286</v>
+        <v>116167</v>
       </c>
       <c r="C10" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3752174</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4371218</v>
+        <v>112860</v>
       </c>
       <c r="F10" t="n">
-        <v>4654460</v>
+        <v>116167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>968020</v>
+        <v>125400</v>
       </c>
       <c r="B11" t="n">
-        <v>1006969</v>
+        <v>129544</v>
       </c>
       <c r="C11" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>3784947</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4468020</v>
+        <v>125400</v>
       </c>
       <c r="F11" t="n">
-        <v>4791916</v>
+        <v>129544</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1064822</v>
+        <v>137940</v>
       </c>
       <c r="B12" t="n">
-        <v>1112566</v>
+        <v>143018</v>
       </c>
       <c r="C12" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>3818006</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>4564822</v>
+        <v>137940</v>
       </c>
       <c r="F12" t="n">
-        <v>4930572</v>
+        <v>143018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1161624</v>
+        <v>150480</v>
       </c>
       <c r="B13" t="n">
-        <v>1219086</v>
+        <v>156589</v>
       </c>
       <c r="C13" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3851354</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4661624</v>
+        <v>150480</v>
       </c>
       <c r="F13" t="n">
-        <v>5070440</v>
+        <v>156589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1258426</v>
+        <v>163647</v>
       </c>
       <c r="B14" t="n">
-        <v>1326536</v>
+        <v>170885</v>
       </c>
       <c r="C14" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3884994</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>4758426</v>
+        <v>163647</v>
       </c>
       <c r="F14" t="n">
-        <v>5211530</v>
+        <v>170885</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1355228</v>
+        <v>176814</v>
       </c>
       <c r="B15" t="n">
-        <v>1434925</v>
+        <v>185284</v>
       </c>
       <c r="C15" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3918927</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4855228</v>
+        <v>176814</v>
       </c>
       <c r="F15" t="n">
-        <v>5353852</v>
+        <v>185284</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1452030</v>
+        <v>189981</v>
       </c>
       <c r="B16" t="n">
-        <v>1544260</v>
+        <v>199786</v>
       </c>
       <c r="C16" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3953157</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>4952030</v>
+        <v>189981</v>
       </c>
       <c r="F16" t="n">
-        <v>5497417</v>
+        <v>199786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1548832</v>
+        <v>203148</v>
       </c>
       <c r="B17" t="n">
-        <v>1654550</v>
+        <v>214393</v>
       </c>
       <c r="C17" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3987686</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>5048832</v>
+        <v>203148</v>
       </c>
       <c r="F17" t="n">
-        <v>5642236</v>
+        <v>214393</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1645634</v>
+        <v>216315</v>
       </c>
       <c r="B18" t="n">
-        <v>1765804</v>
+        <v>229105</v>
       </c>
       <c r="C18" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4022516</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>5145634</v>
+        <v>216315</v>
       </c>
       <c r="F18" t="n">
-        <v>5788320</v>
+        <v>229105</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1742436</v>
+        <v>229482</v>
       </c>
       <c r="B19" t="n">
-        <v>1878030</v>
+        <v>243923</v>
       </c>
       <c r="C19" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4057651</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5242436</v>
+        <v>229482</v>
       </c>
       <c r="F19" t="n">
-        <v>5935681</v>
+        <v>243923</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1839238</v>
+        <v>242649</v>
       </c>
       <c r="B20" t="n">
-        <v>1991236</v>
+        <v>258848</v>
       </c>
       <c r="C20" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4093092</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>5339238</v>
+        <v>242649</v>
       </c>
       <c r="F20" t="n">
-        <v>6084328</v>
+        <v>258848</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1936040</v>
+        <v>255816</v>
       </c>
       <c r="B21" t="n">
-        <v>2105431</v>
+        <v>273881</v>
       </c>
       <c r="C21" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4128843</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>5436040</v>
+        <v>255816</v>
       </c>
       <c r="F21" t="n">
-        <v>6234274</v>
+        <v>273881</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2032842</v>
+        <v>268983</v>
       </c>
       <c r="B22" t="n">
-        <v>2220623</v>
+        <v>289022</v>
       </c>
       <c r="C22" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>4164906</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>5532842</v>
+        <v>268983</v>
       </c>
       <c r="F22" t="n">
-        <v>6385529</v>
+        <v>289022</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2129644</v>
+        <v>282150</v>
       </c>
       <c r="B23" t="n">
-        <v>2336821</v>
+        <v>304272</v>
       </c>
       <c r="C23" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4201284</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>5629644</v>
+        <v>282150</v>
       </c>
       <c r="F23" t="n">
-        <v>6538105</v>
+        <v>304272</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2226446</v>
+        <v>295317</v>
       </c>
       <c r="B24" t="n">
-        <v>2454034</v>
+        <v>319632</v>
       </c>
       <c r="C24" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4237980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>5726446</v>
+        <v>295317</v>
       </c>
       <c r="F24" t="n">
-        <v>6692014</v>
+        <v>319632</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2323248</v>
+        <v>308484</v>
       </c>
       <c r="B25" t="n">
-        <v>2572271</v>
+        <v>335103</v>
       </c>
       <c r="C25" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>4274997</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>5823248</v>
+        <v>308484</v>
       </c>
       <c r="F25" t="n">
-        <v>6847268</v>
+        <v>335103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2420050</v>
+        <v>322309</v>
       </c>
       <c r="B26" t="n">
-        <v>2691541</v>
+        <v>351343</v>
       </c>
       <c r="C26" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>4312337</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>5920050</v>
+        <v>322309</v>
       </c>
       <c r="F26" t="n">
-        <v>7003878</v>
+        <v>351343</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2516852</v>
+        <v>336134</v>
       </c>
       <c r="B27" t="n">
-        <v>2811853</v>
+        <v>367700</v>
       </c>
       <c r="C27" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>4350003</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>6016852</v>
+        <v>336134</v>
       </c>
       <c r="F27" t="n">
-        <v>7161856</v>
+        <v>367700</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2613654</v>
+        <v>349959</v>
       </c>
       <c r="B28" t="n">
-        <v>2933215</v>
+        <v>384175</v>
       </c>
       <c r="C28" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>4387998</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>6113654</v>
+        <v>349959</v>
       </c>
       <c r="F28" t="n">
-        <v>7321213</v>
+        <v>384175</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2710456</v>
+        <v>363784</v>
       </c>
       <c r="B29" t="n">
-        <v>3055637</v>
+        <v>400769</v>
       </c>
       <c r="C29" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>4426325</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>6210456</v>
+        <v>363784</v>
       </c>
       <c r="F29" t="n">
-        <v>7481962</v>
+        <v>400769</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2807258</v>
+        <v>377609</v>
       </c>
       <c r="B30" t="n">
-        <v>3179129</v>
+        <v>417482</v>
       </c>
       <c r="C30" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>4464987</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>6307258</v>
+        <v>377609</v>
       </c>
       <c r="F30" t="n">
-        <v>7644116</v>
+        <v>417482</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2904060</v>
+        <v>391434</v>
       </c>
       <c r="B31" t="n">
-        <v>3303699</v>
+        <v>434316</v>
       </c>
       <c r="C31" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>4503986</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>6404060</v>
+        <v>391434</v>
       </c>
       <c r="F31" t="n">
-        <v>7807685</v>
+        <v>434316</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3000862</v>
+        <v>405259</v>
       </c>
       <c r="B32" t="n">
-        <v>3429357</v>
+        <v>451271</v>
       </c>
       <c r="C32" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>4543326</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>6500862</v>
+        <v>405259</v>
       </c>
       <c r="F32" t="n">
-        <v>7972683</v>
+        <v>451271</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3097664</v>
+        <v>419084</v>
       </c>
       <c r="B33" t="n">
-        <v>3556113</v>
+        <v>468348</v>
       </c>
       <c r="C33" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>4583010</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>6597664</v>
+        <v>419084</v>
       </c>
       <c r="F33" t="n">
-        <v>8139123</v>
+        <v>468348</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3194466</v>
+        <v>432909</v>
       </c>
       <c r="B34" t="n">
-        <v>3683976</v>
+        <v>485549</v>
       </c>
       <c r="C34" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>4623040</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6694466</v>
+        <v>432909</v>
       </c>
       <c r="F34" t="n">
-        <v>8307016</v>
+        <v>485549</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3291268</v>
+        <v>446734</v>
       </c>
       <c r="B35" t="n">
-        <v>3812956</v>
+        <v>502874</v>
       </c>
       <c r="C35" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>4663420</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>6791268</v>
+        <v>446734</v>
       </c>
       <c r="F35" t="n">
-        <v>8476376</v>
+        <v>502874</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3388070</v>
+        <v>460559</v>
       </c>
       <c r="B36" t="n">
-        <v>3943063</v>
+        <v>520323</v>
       </c>
       <c r="C36" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>4704153</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>6888070</v>
+        <v>460559</v>
       </c>
       <c r="F36" t="n">
-        <v>8647216</v>
+        <v>520323</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3484872</v>
+        <v>474384</v>
       </c>
       <c r="B37" t="n">
-        <v>4074306</v>
+        <v>537898</v>
       </c>
       <c r="C37" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>4745241</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>6984872</v>
+        <v>474384</v>
       </c>
       <c r="F37" t="n">
-        <v>8819547</v>
+        <v>537898</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3581674</v>
+        <v>488901</v>
       </c>
       <c r="B38" t="n">
-        <v>4206695</v>
+        <v>556292</v>
       </c>
       <c r="C38" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>4786688</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>7081674</v>
+        <v>488901</v>
       </c>
       <c r="F38" t="n">
-        <v>8993383</v>
+        <v>556292</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3678476</v>
+        <v>503418</v>
       </c>
       <c r="B39" t="n">
-        <v>4340241</v>
+        <v>574818</v>
       </c>
       <c r="C39" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>4828497</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>7178476</v>
+        <v>503418</v>
       </c>
       <c r="F39" t="n">
-        <v>9168738</v>
+        <v>574818</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3775278</v>
+        <v>517935</v>
       </c>
       <c r="B40" t="n">
-        <v>4474953</v>
+        <v>593478</v>
       </c>
       <c r="C40" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4870671</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7275278</v>
+        <v>517935</v>
       </c>
       <c r="F40" t="n">
-        <v>9345624</v>
+        <v>593478</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3872080</v>
+        <v>532452</v>
       </c>
       <c r="B41" t="n">
-        <v>4610842</v>
+        <v>612272</v>
       </c>
       <c r="C41" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>4913214</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>7372080</v>
+        <v>532452</v>
       </c>
       <c r="F41" t="n">
-        <v>9524056</v>
+        <v>612272</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3968882</v>
+        <v>546969</v>
       </c>
       <c r="B42" t="n">
-        <v>4747918</v>
+        <v>631202</v>
       </c>
       <c r="C42" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>4956128</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>7468882</v>
+        <v>546969</v>
       </c>
       <c r="F42" t="n">
-        <v>9704046</v>
+        <v>631202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4065684</v>
+        <v>561486</v>
       </c>
       <c r="B43" t="n">
-        <v>4886191</v>
+        <v>650268</v>
       </c>
       <c r="C43" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>4999417</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7565684</v>
+        <v>561486</v>
       </c>
       <c r="F43" t="n">
-        <v>9885608</v>
+        <v>650268</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>4162486</v>
+        <v>576003</v>
       </c>
       <c r="B44" t="n">
-        <v>5025672</v>
+        <v>669472</v>
       </c>
       <c r="C44" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>5043084</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>7662486</v>
+        <v>576003</v>
       </c>
       <c r="F44" t="n">
-        <v>10068756</v>
+        <v>669472</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4259288</v>
+        <v>590520</v>
       </c>
       <c r="B45" t="n">
-        <v>5166371</v>
+        <v>688814</v>
       </c>
       <c r="C45" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>5087133</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>7759288</v>
+        <v>590520</v>
       </c>
       <c r="F45" t="n">
-        <v>10253504</v>
+        <v>688814</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4356090</v>
+        <v>605037</v>
       </c>
       <c r="B46" t="n">
-        <v>5308299</v>
+        <v>708296</v>
       </c>
       <c r="C46" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>5131567</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>7856090</v>
+        <v>605037</v>
       </c>
       <c r="F46" t="n">
-        <v>10439866</v>
+        <v>708296</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4452892</v>
+        <v>619554</v>
       </c>
       <c r="B47" t="n">
-        <v>5451467</v>
+        <v>727918</v>
       </c>
       <c r="C47" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>5176389</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>7952892</v>
+        <v>619554</v>
       </c>
       <c r="F47" t="n">
-        <v>10627856</v>
+        <v>727918</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4549694</v>
+        <v>634071</v>
       </c>
       <c r="B48" t="n">
-        <v>5595885</v>
+        <v>747681</v>
       </c>
       <c r="C48" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>5221602</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>8049694</v>
+        <v>634071</v>
       </c>
       <c r="F48" t="n">
-        <v>10817487</v>
+        <v>747681</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4646496</v>
+        <v>648588</v>
       </c>
       <c r="B49" t="n">
-        <v>5741565</v>
+        <v>767587</v>
       </c>
       <c r="C49" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>5267210</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>8146496</v>
+        <v>648588</v>
       </c>
       <c r="F49" t="n">
-        <v>11008775</v>
+        <v>767587</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4743298</v>
+        <v>663830</v>
       </c>
       <c r="B50" t="n">
-        <v>5888517</v>
+        <v>788361</v>
       </c>
       <c r="C50" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>5313216</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>8243298</v>
+        <v>663830</v>
       </c>
       <c r="F50" t="n">
-        <v>11201733</v>
+        <v>788361</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4840100</v>
+        <v>679072</v>
       </c>
       <c r="B51" t="n">
-        <v>6036753</v>
+        <v>809285</v>
       </c>
       <c r="C51" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>5359624</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>8340100</v>
+        <v>679072</v>
       </c>
       <c r="F51" t="n">
-        <v>11396377</v>
+        <v>809285</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4936902</v>
+        <v>694314</v>
       </c>
       <c r="B52" t="n">
-        <v>6186284</v>
+        <v>830360</v>
       </c>
       <c r="C52" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>5406438</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>8436902</v>
+        <v>694314</v>
       </c>
       <c r="F52" t="n">
-        <v>11592722</v>
+        <v>830360</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5033704</v>
+        <v>709556</v>
       </c>
       <c r="B53" t="n">
-        <v>6337121</v>
+        <v>851587</v>
       </c>
       <c r="C53" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>5453661</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>8533704</v>
+        <v>709556</v>
       </c>
       <c r="F53" t="n">
-        <v>11790782</v>
+        <v>851587</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>5130506</v>
+        <v>724798</v>
       </c>
       <c r="B54" t="n">
-        <v>6489275</v>
+        <v>872967</v>
       </c>
       <c r="C54" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>5501296</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>8630506</v>
+        <v>724798</v>
       </c>
       <c r="F54" t="n">
-        <v>11990571</v>
+        <v>872967</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>5227308</v>
+        <v>740040</v>
       </c>
       <c r="B55" t="n">
-        <v>6642758</v>
+        <v>894501</v>
       </c>
       <c r="C55" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>5549347</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>8727308</v>
+        <v>740040</v>
       </c>
       <c r="F55" t="n">
-        <v>12192105</v>
+        <v>894501</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5324110</v>
+        <v>755282</v>
       </c>
       <c r="B56" t="n">
-        <v>6797582</v>
+        <v>916190</v>
       </c>
       <c r="C56" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>5597818</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>8824110</v>
+        <v>755282</v>
       </c>
       <c r="F56" t="n">
-        <v>12395400</v>
+        <v>916190</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>5420912</v>
+        <v>770524</v>
       </c>
       <c r="B57" t="n">
-        <v>6953758</v>
+        <v>938035</v>
       </c>
       <c r="C57" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>5646712</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>8920912</v>
+        <v>770524</v>
       </c>
       <c r="F57" t="n">
-        <v>12600470</v>
+        <v>938035</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>5517714</v>
+        <v>785766</v>
       </c>
       <c r="B58" t="n">
-        <v>7111298</v>
+        <v>960038</v>
       </c>
       <c r="C58" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>5696033</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>9017714</v>
+        <v>785766</v>
       </c>
       <c r="F58" t="n">
-        <v>12807331</v>
+        <v>960038</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5614516</v>
+        <v>801008</v>
       </c>
       <c r="B59" t="n">
-        <v>7270214</v>
+        <v>982199</v>
       </c>
       <c r="C59" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>5745785</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>9114516</v>
+        <v>801008</v>
       </c>
       <c r="F59" t="n">
-        <v>13015999</v>
+        <v>982199</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5711318</v>
+        <v>816250</v>
       </c>
       <c r="B60" t="n">
-        <v>7430518</v>
+        <v>1004520</v>
       </c>
       <c r="C60" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>5795972</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>9211318</v>
+        <v>816250</v>
       </c>
       <c r="F60" t="n">
-        <v>13226490</v>
+        <v>1004520</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5808120</v>
+        <v>831492</v>
       </c>
       <c r="B61" t="n">
-        <v>7592223</v>
+        <v>1027002</v>
       </c>
       <c r="C61" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>5846597</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>9308120</v>
+        <v>831492</v>
       </c>
       <c r="F61" t="n">
-        <v>13438820</v>
+        <v>1027002</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5904922</v>
+        <v>847497</v>
       </c>
       <c r="B62" t="n">
-        <v>7755340</v>
+        <v>1050409</v>
       </c>
       <c r="C62" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>5897664</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>9404922</v>
+        <v>847497</v>
       </c>
       <c r="F62" t="n">
-        <v>13653004</v>
+        <v>1050409</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6001724</v>
+        <v>863502</v>
       </c>
       <c r="B63" t="n">
-        <v>7919882</v>
+        <v>1073985</v>
       </c>
       <c r="C63" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>5949177</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>9501724</v>
+        <v>863502</v>
       </c>
       <c r="F63" t="n">
-        <v>13869059</v>
+        <v>1073985</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>6098526</v>
+        <v>879507</v>
       </c>
       <c r="B64" t="n">
-        <v>8085861</v>
+        <v>1097731</v>
       </c>
       <c r="C64" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>6001140</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9598526</v>
+        <v>879507</v>
       </c>
       <c r="F64" t="n">
-        <v>14087001</v>
+        <v>1097731</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6195328</v>
+        <v>895512</v>
       </c>
       <c r="B65" t="n">
-        <v>8253290</v>
+        <v>1121648</v>
       </c>
       <c r="C65" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>6053557</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>9695328</v>
+        <v>895512</v>
       </c>
       <c r="F65" t="n">
-        <v>14306847</v>
+        <v>1121648</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>6292130</v>
+        <v>911517</v>
       </c>
       <c r="B66" t="n">
-        <v>8422181</v>
+        <v>1145737</v>
       </c>
       <c r="C66" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>6106432</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>9792130</v>
+        <v>911517</v>
       </c>
       <c r="F66" t="n">
-        <v>14528613</v>
+        <v>1145737</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>6388932</v>
+        <v>927522</v>
       </c>
       <c r="B67" t="n">
-        <v>8592547</v>
+        <v>1170000</v>
       </c>
       <c r="C67" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>6159769</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>9888932</v>
+        <v>927522</v>
       </c>
       <c r="F67" t="n">
-        <v>14752316</v>
+        <v>1170000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6485734</v>
+        <v>943527</v>
       </c>
       <c r="B68" t="n">
-        <v>8764401</v>
+        <v>1194438</v>
       </c>
       <c r="C68" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>6213572</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>9985734</v>
+        <v>943527</v>
       </c>
       <c r="F68" t="n">
-        <v>14977973</v>
+        <v>1194438</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>6582536</v>
+        <v>959532</v>
       </c>
       <c r="B69" t="n">
-        <v>8937756</v>
+        <v>1219052</v>
       </c>
       <c r="C69" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>6267845</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>10082536</v>
+        <v>959532</v>
       </c>
       <c r="F69" t="n">
-        <v>15205601</v>
+        <v>1219052</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6679338</v>
+        <v>975537</v>
       </c>
       <c r="B70" t="n">
-        <v>9112626</v>
+        <v>1243843</v>
       </c>
       <c r="C70" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>6322592</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>10179338</v>
+        <v>975537</v>
       </c>
       <c r="F70" t="n">
-        <v>15435218</v>
+        <v>1243843</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>6776140</v>
+        <v>991542</v>
       </c>
       <c r="B71" t="n">
-        <v>9289023</v>
+        <v>1268813</v>
       </c>
       <c r="C71" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>6377817</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>10276140</v>
+        <v>991542</v>
       </c>
       <c r="F71" t="n">
-        <v>15666840</v>
+        <v>1268813</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>6872942</v>
+        <v>1007547</v>
       </c>
       <c r="B72" t="n">
-        <v>9466961</v>
+        <v>1293963</v>
       </c>
       <c r="C72" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>6433524</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>10372942</v>
+        <v>1007547</v>
       </c>
       <c r="F72" t="n">
-        <v>15900485</v>
+        <v>1293963</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6969744</v>
+        <v>1023552</v>
       </c>
       <c r="B73" t="n">
-        <v>9646453</v>
+        <v>1319294</v>
       </c>
       <c r="C73" t="n">
-        <v>3500000</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>6489718</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>10469744</v>
+        <v>1023552</v>
       </c>
       <c r="F73" t="n">
-        <v>16136171</v>
+        <v>1319294</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1040357</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1345608</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1040357</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1345608</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1057162</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1372111</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1057162</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1372111</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1073967</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1398805</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1073967</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1398805</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1090772</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1425692</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1090772</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1425692</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1107577</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1452772</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1107577</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1452772</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1124382</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1480048</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1124382</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1480048</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1141187</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1507520</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1141187</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1507520</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1157992</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1535190</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1157992</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1535190</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1174797</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1563060</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1174797</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1563060</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1191602</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1591130</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1191602</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1591130</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1208407</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1619403</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1208407</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1619403</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1225212</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1647880</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1225212</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1647880</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1242857</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1677402</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1242857</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1677402</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1260502</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1707137</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1260502</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1707137</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1278147</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1737086</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1278147</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1737086</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1295792</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1767251</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1295792</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1767251</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1313437</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1797633</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1313437</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1797633</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1331082</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1828234</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1331082</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1828234</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1348727</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1859056</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1348727</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1859056</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1366372</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1890100</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1366372</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1890100</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1384017</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1921368</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1384017</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1921368</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1401662</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1952861</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1401662</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1952861</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1419307</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1984581</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1419307</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1984581</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1436952</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2016530</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1436952</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2016530</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1455479</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2049591</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1455479</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2049591</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1474006</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2082890</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1474006</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2082890</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1492533</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2116429</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1492533</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2116429</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1511060</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2150210</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1511060</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2150210</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1529587</v>
+      </c>
+      <c r="B102" t="n">
+        <v>2184234</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1529587</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2184234</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1548114</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2218503</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1548114</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2218503</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1566641</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2253019</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1566641</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2253019</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1585168</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2287784</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1585168</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2287784</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1603695</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2322800</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1603695</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2322800</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1622222</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2358068</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1622222</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2358068</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1640749</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2393590</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1640749</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2393590</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1659276</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2429368</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1659276</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2429368</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1678730</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2466331</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1678730</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2466331</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1698184</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2503561</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1698184</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2503561</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1717638</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2541059</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1717638</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2541059</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1737092</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2578827</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1737092</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2578827</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1756546</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2616867</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1756546</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2616867</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1776000</v>
+      </c>
+      <c r="B115" t="n">
+        <v>2655182</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1776000</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2655182</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1795454</v>
+      </c>
+      <c r="B116" t="n">
+        <v>2693773</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1795454</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2693773</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1814908</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2732642</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1814908</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2732642</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1834362</v>
+      </c>
+      <c r="B118" t="n">
+        <v>2771791</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1834362</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2771791</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1853816</v>
+      </c>
+      <c r="B119" t="n">
+        <v>2811222</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1853816</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2811222</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1873270</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2850937</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1873270</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2850937</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1892724</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2890939</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1892724</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2890939</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1913150</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2932201</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1913150</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2932201</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1933576</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2973760</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1933576</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2973760</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1954002</v>
+      </c>
+      <c r="B124" t="n">
+        <v>3015619</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1954002</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3015619</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1974428</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3057780</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1974428</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3057780</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1994854</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3100244</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1994854</v>
+      </c>
+      <c r="F126" t="n">
+        <v>3100244</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2015280</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3143014</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2015280</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3143014</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2035706</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3186093</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2035706</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3186093</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2056132</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3229482</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2056132</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3229482</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2076558</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3273184</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2076558</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3273184</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2096984</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3317201</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2096984</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3317201</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2117410</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3361535</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2117410</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3361535</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2137836</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3406189</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2137836</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3406189</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2159284</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3452187</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2159284</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3452187</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2180732</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3498516</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2180732</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3498516</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2202180</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3545179</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2202180</v>
+      </c>
+      <c r="F136" t="n">
+        <v>3545179</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2223628</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3592178</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2223628</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3592178</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2245076</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3639516</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2245076</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3639516</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2266524</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3687195</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2266524</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3687195</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2287972</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3735218</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2287972</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3735218</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2309420</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3783587</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2309420</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3783587</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2330868</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3832305</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2330868</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3832305</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2352316</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3881374</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2352316</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3881374</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2373764</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3930796</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2373764</v>
+      </c>
+      <c r="F144" t="n">
+        <v>3930796</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2395212</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3980575</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2395212</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3980575</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2417732</v>
+      </c>
+      <c r="B146" t="n">
+        <v>4031784</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2417732</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4031784</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2440252</v>
+      </c>
+      <c r="B147" t="n">
+        <v>4083362</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2440252</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4083362</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2462772</v>
+      </c>
+      <c r="B148" t="n">
+        <v>4135312</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2462772</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4135312</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2485292</v>
+      </c>
+      <c r="B149" t="n">
+        <v>4187637</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2485292</v>
+      </c>
+      <c r="F149" t="n">
+        <v>4187637</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2507812</v>
+      </c>
+      <c r="B150" t="n">
+        <v>4240339</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2507812</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4240339</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2530332</v>
+      </c>
+      <c r="B151" t="n">
+        <v>4293420</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2530332</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4293420</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2552852</v>
+      </c>
+      <c r="B152" t="n">
+        <v>4346884</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2552852</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4346884</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2575372</v>
+      </c>
+      <c r="B153" t="n">
+        <v>4400733</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2575372</v>
+      </c>
+      <c r="F153" t="n">
+        <v>4400733</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2597892</v>
+      </c>
+      <c r="B154" t="n">
+        <v>4454971</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2597892</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4454971</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2620412</v>
+      </c>
+      <c r="B155" t="n">
+        <v>4509599</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2620412</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4509599</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2642932</v>
+      </c>
+      <c r="B156" t="n">
+        <v>4564621</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2642932</v>
+      </c>
+      <c r="F156" t="n">
+        <v>4564621</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2665452</v>
+      </c>
+      <c r="B157" t="n">
+        <v>4620040</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2665452</v>
+      </c>
+      <c r="F157" t="n">
+        <v>4620040</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2689098</v>
+      </c>
+      <c r="B158" t="n">
+        <v>4676984</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2689098</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4676984</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2712744</v>
+      </c>
+      <c r="B159" t="n">
+        <v>4734339</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2712744</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4734339</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2736390</v>
+      </c>
+      <c r="B160" t="n">
+        <v>4792107</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2736390</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4792107</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2760036</v>
+      </c>
+      <c r="B161" t="n">
+        <v>4850291</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2760036</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4850291</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2783682</v>
+      </c>
+      <c r="B162" t="n">
+        <v>4908895</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2783682</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4908895</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2807328</v>
+      </c>
+      <c r="B163" t="n">
+        <v>4967921</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2807328</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4967921</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2830974</v>
+      </c>
+      <c r="B164" t="n">
+        <v>5027372</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2830974</v>
+      </c>
+      <c r="F164" t="n">
+        <v>5027372</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2854620</v>
+      </c>
+      <c r="B165" t="n">
+        <v>5087252</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2854620</v>
+      </c>
+      <c r="F165" t="n">
+        <v>5087252</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2878266</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5147563</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2878266</v>
+      </c>
+      <c r="F166" t="n">
+        <v>5147563</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2901912</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5208309</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2901912</v>
+      </c>
+      <c r="F167" t="n">
+        <v>5208309</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2925558</v>
+      </c>
+      <c r="B168" t="n">
+        <v>5269493</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2925558</v>
+      </c>
+      <c r="F168" t="n">
+        <v>5269493</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2949204</v>
+      </c>
+      <c r="B169" t="n">
+        <v>5331118</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2949204</v>
+      </c>
+      <c r="F169" t="n">
+        <v>5331118</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2974032</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5394369</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2974032</v>
+      </c>
+      <c r="F170" t="n">
+        <v>5394369</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2998860</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5458076</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2998860</v>
+      </c>
+      <c r="F171" t="n">
+        <v>5458076</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>3023688</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5522242</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3023688</v>
+      </c>
+      <c r="F172" t="n">
+        <v>5522242</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>3048516</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5586871</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3048516</v>
+      </c>
+      <c r="F173" t="n">
+        <v>5586871</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>3073344</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5651965</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3073344</v>
+      </c>
+      <c r="F174" t="n">
+        <v>5651965</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>3098172</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5717529</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3098172</v>
+      </c>
+      <c r="F175" t="n">
+        <v>5717529</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>3123000</v>
+      </c>
+      <c r="B176" t="n">
+        <v>5783565</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3123000</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5783565</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>3147828</v>
+      </c>
+      <c r="B177" t="n">
+        <v>5850077</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3147828</v>
+      </c>
+      <c r="F177" t="n">
+        <v>5850077</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>3172656</v>
+      </c>
+      <c r="B178" t="n">
+        <v>5917068</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3172656</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5917068</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>3197484</v>
+      </c>
+      <c r="B179" t="n">
+        <v>5984542</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3197484</v>
+      </c>
+      <c r="F179" t="n">
+        <v>5984542</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>3222312</v>
+      </c>
+      <c r="B180" t="n">
+        <v>6052503</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3222312</v>
+      </c>
+      <c r="F180" t="n">
+        <v>6052503</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>3247140</v>
+      </c>
+      <c r="B181" t="n">
+        <v>6120953</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3247140</v>
+      </c>
+      <c r="F181" t="n">
+        <v>6120953</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>3273210</v>
+      </c>
+      <c r="B182" t="n">
+        <v>6191139</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>3273210</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6191139</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>3299280</v>
+      </c>
+      <c r="B183" t="n">
+        <v>6261831</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3299280</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6261831</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>3325350</v>
+      </c>
+      <c r="B184" t="n">
+        <v>6333032</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3325350</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6333032</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>3351420</v>
+      </c>
+      <c r="B185" t="n">
+        <v>6404746</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>3351420</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6404746</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>3377490</v>
+      </c>
+      <c r="B186" t="n">
+        <v>6476977</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>3377490</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6476977</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>3403560</v>
+      </c>
+      <c r="B187" t="n">
+        <v>6549729</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3403560</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6549729</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>3429630</v>
+      </c>
+      <c r="B188" t="n">
+        <v>6623005</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3429630</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6623005</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>3455700</v>
+      </c>
+      <c r="B189" t="n">
+        <v>6696809</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3455700</v>
+      </c>
+      <c r="F189" t="n">
+        <v>6696809</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>3481770</v>
+      </c>
+      <c r="B190" t="n">
+        <v>6771145</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3481770</v>
+      </c>
+      <c r="F190" t="n">
+        <v>6771145</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>3507840</v>
+      </c>
+      <c r="B191" t="n">
+        <v>6846017</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3507840</v>
+      </c>
+      <c r="F191" t="n">
+        <v>6846017</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>3533910</v>
+      </c>
+      <c r="B192" t="n">
+        <v>6921428</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3533910</v>
+      </c>
+      <c r="F192" t="n">
+        <v>6921428</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>3559980</v>
+      </c>
+      <c r="B193" t="n">
+        <v>6997383</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3559980</v>
+      </c>
+      <c r="F193" t="n">
+        <v>6997383</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>3587353</v>
+      </c>
+      <c r="B194" t="n">
+        <v>7075188</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3587353</v>
+      </c>
+      <c r="F194" t="n">
+        <v>7075188</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>3614726</v>
+      </c>
+      <c r="B195" t="n">
+        <v>7153554</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3614726</v>
+      </c>
+      <c r="F195" t="n">
+        <v>7153554</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>3642099</v>
+      </c>
+      <c r="B196" t="n">
+        <v>7232485</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3642099</v>
+      </c>
+      <c r="F196" t="n">
+        <v>7232485</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>3669472</v>
+      </c>
+      <c r="B197" t="n">
+        <v>7311985</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3669472</v>
+      </c>
+      <c r="F197" t="n">
+        <v>7311985</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>3696845</v>
+      </c>
+      <c r="B198" t="n">
+        <v>7392058</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3696845</v>
+      </c>
+      <c r="F198" t="n">
+        <v>7392058</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>3724218</v>
+      </c>
+      <c r="B199" t="n">
+        <v>7472708</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3724218</v>
+      </c>
+      <c r="F199" t="n">
+        <v>7472708</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3751591</v>
+      </c>
+      <c r="B200" t="n">
+        <v>7553939</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3751591</v>
+      </c>
+      <c r="F200" t="n">
+        <v>7553939</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3778964</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7635756</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>3778964</v>
+      </c>
+      <c r="F201" t="n">
+        <v>7635756</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>3806337</v>
+      </c>
+      <c r="B202" t="n">
+        <v>7718162</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>3806337</v>
+      </c>
+      <c r="F202" t="n">
+        <v>7718162</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3833710</v>
+      </c>
+      <c r="B203" t="n">
+        <v>7801162</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3833710</v>
+      </c>
+      <c r="F203" t="n">
+        <v>7801162</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>3861083</v>
+      </c>
+      <c r="B204" t="n">
+        <v>7884760</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3861083</v>
+      </c>
+      <c r="F204" t="n">
+        <v>7884760</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3888456</v>
+      </c>
+      <c r="B205" t="n">
+        <v>7968961</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3888456</v>
+      </c>
+      <c r="F205" t="n">
+        <v>7968961</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3917198</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8055138</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3917198</v>
+      </c>
+      <c r="F206" t="n">
+        <v>8055138</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3945940</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8141936</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3945940</v>
+      </c>
+      <c r="F207" t="n">
+        <v>8141936</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3974682</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8229360</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3974682</v>
+      </c>
+      <c r="F208" t="n">
+        <v>8229360</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>4003424</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8317414</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>4003424</v>
+      </c>
+      <c r="F209" t="n">
+        <v>8317414</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4032166</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8406102</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>4032166</v>
+      </c>
+      <c r="F210" t="n">
+        <v>8406102</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4060908</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8495429</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4060908</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8495429</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4089650</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8585400</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>4089650</v>
+      </c>
+      <c r="F212" t="n">
+        <v>8585400</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4118392</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8676020</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>4118392</v>
+      </c>
+      <c r="F213" t="n">
+        <v>8676020</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4147134</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8767293</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>4147134</v>
+      </c>
+      <c r="F214" t="n">
+        <v>8767293</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4175876</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8859224</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4175876</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8859224</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4204618</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8951817</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4204618</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8951817</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4233360</v>
+      </c>
+      <c r="B217" t="n">
+        <v>9045078</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>4233360</v>
+      </c>
+      <c r="F217" t="n">
+        <v>9045078</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4263539</v>
+      </c>
+      <c r="B218" t="n">
+        <v>9140448</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>4263539</v>
+      </c>
+      <c r="F218" t="n">
+        <v>9140448</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4293718</v>
+      </c>
+      <c r="B219" t="n">
+        <v>9236505</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>4293718</v>
+      </c>
+      <c r="F219" t="n">
+        <v>9236505</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>4323897</v>
+      </c>
+      <c r="B220" t="n">
+        <v>9333254</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4323897</v>
+      </c>
+      <c r="F220" t="n">
+        <v>9333254</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4354076</v>
+      </c>
+      <c r="B221" t="n">
+        <v>9430701</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>4354076</v>
+      </c>
+      <c r="F221" t="n">
+        <v>9430701</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>4384255</v>
+      </c>
+      <c r="B222" t="n">
+        <v>9528850</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4384255</v>
+      </c>
+      <c r="F222" t="n">
+        <v>9528850</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>4414434</v>
+      </c>
+      <c r="B223" t="n">
+        <v>9627707</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>4414434</v>
+      </c>
+      <c r="F223" t="n">
+        <v>9627707</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>4444613</v>
+      </c>
+      <c r="B224" t="n">
+        <v>9727276</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4444613</v>
+      </c>
+      <c r="F224" t="n">
+        <v>9727276</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>4474792</v>
+      </c>
+      <c r="B225" t="n">
+        <v>9827563</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4474792</v>
+      </c>
+      <c r="F225" t="n">
+        <v>9827563</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>4504971</v>
+      </c>
+      <c r="B226" t="n">
+        <v>9928572</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4504971</v>
+      </c>
+      <c r="F226" t="n">
+        <v>9928572</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>4535150</v>
+      </c>
+      <c r="B227" t="n">
+        <v>10030309</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4535150</v>
+      </c>
+      <c r="F227" t="n">
+        <v>10030309</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>4565329</v>
+      </c>
+      <c r="B228" t="n">
+        <v>10132780</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>4565329</v>
+      </c>
+      <c r="F228" t="n">
+        <v>10132780</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>4595508</v>
+      </c>
+      <c r="B229" t="n">
+        <v>10235989</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4595508</v>
+      </c>
+      <c r="F229" t="n">
+        <v>10235989</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>4627196</v>
+      </c>
+      <c r="B230" t="n">
+        <v>10341451</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4627196</v>
+      </c>
+      <c r="F230" t="n">
+        <v>10341451</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>4658884</v>
+      </c>
+      <c r="B231" t="n">
+        <v>10447673</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>4658884</v>
+      </c>
+      <c r="F231" t="n">
+        <v>10447673</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>4690572</v>
+      </c>
+      <c r="B232" t="n">
+        <v>10554661</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>4690572</v>
+      </c>
+      <c r="F232" t="n">
+        <v>10554661</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>4722260</v>
+      </c>
+      <c r="B233" t="n">
+        <v>10662420</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>4722260</v>
+      </c>
+      <c r="F233" t="n">
+        <v>10662420</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>4753948</v>
+      </c>
+      <c r="B234" t="n">
+        <v>10770956</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>4753948</v>
+      </c>
+      <c r="F234" t="n">
+        <v>10770956</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>4785636</v>
+      </c>
+      <c r="B235" t="n">
+        <v>10880274</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>4785636</v>
+      </c>
+      <c r="F235" t="n">
+        <v>10880274</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>4817324</v>
+      </c>
+      <c r="B236" t="n">
+        <v>10990380</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>4817324</v>
+      </c>
+      <c r="F236" t="n">
+        <v>10990380</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>4849012</v>
+      </c>
+      <c r="B237" t="n">
+        <v>11101279</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>4849012</v>
+      </c>
+      <c r="F237" t="n">
+        <v>11101279</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>4880700</v>
+      </c>
+      <c r="B238" t="n">
+        <v>11212978</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>4880700</v>
+      </c>
+      <c r="F238" t="n">
+        <v>11212978</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>4912388</v>
+      </c>
+      <c r="B239" t="n">
+        <v>11325482</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4912388</v>
+      </c>
+      <c r="F239" t="n">
+        <v>11325482</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>4944076</v>
+      </c>
+      <c r="B240" t="n">
+        <v>11438796</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4944076</v>
+      </c>
+      <c r="F240" t="n">
+        <v>11438796</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>4975764</v>
+      </c>
+      <c r="B241" t="n">
+        <v>11552927</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4975764</v>
+      </c>
+      <c r="F241" t="n">
+        <v>11552927</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>5009036</v>
+      </c>
+      <c r="B242" t="n">
+        <v>11669465</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>5009036</v>
+      </c>
+      <c r="F242" t="n">
+        <v>11669465</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>5042308</v>
+      </c>
+      <c r="B243" t="n">
+        <v>11786843</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>5042308</v>
+      </c>
+      <c r="F243" t="n">
+        <v>11786843</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>5075580</v>
+      </c>
+      <c r="B244" t="n">
+        <v>11905067</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>5075580</v>
+      </c>
+      <c r="F244" t="n">
+        <v>11905067</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>5108852</v>
+      </c>
+      <c r="B245" t="n">
+        <v>12024143</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>5108852</v>
+      </c>
+      <c r="F245" t="n">
+        <v>12024143</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>5142124</v>
+      </c>
+      <c r="B246" t="n">
+        <v>12144077</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>5142124</v>
+      </c>
+      <c r="F246" t="n">
+        <v>12144077</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>5175396</v>
+      </c>
+      <c r="B247" t="n">
+        <v>12264875</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>5175396</v>
+      </c>
+      <c r="F247" t="n">
+        <v>12264875</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>5208668</v>
+      </c>
+      <c r="B248" t="n">
+        <v>12386544</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>5208668</v>
+      </c>
+      <c r="F248" t="n">
+        <v>12386544</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>5241940</v>
+      </c>
+      <c r="B249" t="n">
+        <v>12509090</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>5241940</v>
+      </c>
+      <c r="F249" t="n">
+        <v>12509090</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>5275212</v>
+      </c>
+      <c r="B250" t="n">
+        <v>12632519</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>5275212</v>
+      </c>
+      <c r="F250" t="n">
+        <v>12632519</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>5308484</v>
+      </c>
+      <c r="B251" t="n">
+        <v>12756838</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>5308484</v>
+      </c>
+      <c r="F251" t="n">
+        <v>12756838</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>5341756</v>
+      </c>
+      <c r="B252" t="n">
+        <v>12882053</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>5341756</v>
+      </c>
+      <c r="F252" t="n">
+        <v>12882053</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>5375028</v>
+      </c>
+      <c r="B253" t="n">
+        <v>13008170</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>5375028</v>
+      </c>
+      <c r="F253" t="n">
+        <v>13008170</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>5409964</v>
+      </c>
+      <c r="B254" t="n">
+        <v>13136860</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>5409964</v>
+      </c>
+      <c r="F254" t="n">
+        <v>13136860</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>5444900</v>
+      </c>
+      <c r="B255" t="n">
+        <v>13266478</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>5444900</v>
+      </c>
+      <c r="F255" t="n">
+        <v>13266478</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>5479836</v>
+      </c>
+      <c r="B256" t="n">
+        <v>13397030</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>5479836</v>
+      </c>
+      <c r="F256" t="n">
+        <v>13397030</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>5514772</v>
+      </c>
+      <c r="B257" t="n">
+        <v>13528523</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>5514772</v>
+      </c>
+      <c r="F257" t="n">
+        <v>13528523</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>5549708</v>
+      </c>
+      <c r="B258" t="n">
+        <v>13660963</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>5549708</v>
+      </c>
+      <c r="F258" t="n">
+        <v>13660963</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>5584644</v>
+      </c>
+      <c r="B259" t="n">
+        <v>13794358</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>5584644</v>
+      </c>
+      <c r="F259" t="n">
+        <v>13794358</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>5619580</v>
+      </c>
+      <c r="B260" t="n">
+        <v>13928714</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>5619580</v>
+      </c>
+      <c r="F260" t="n">
+        <v>13928714</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>5654516</v>
+      </c>
+      <c r="B261" t="n">
+        <v>14064039</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>5654516</v>
+      </c>
+      <c r="F261" t="n">
+        <v>14064039</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>5689452</v>
+      </c>
+      <c r="B262" t="n">
+        <v>14200339</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>5689452</v>
+      </c>
+      <c r="F262" t="n">
+        <v>14200339</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>5724388</v>
+      </c>
+      <c r="B263" t="n">
+        <v>14337621</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>5724388</v>
+      </c>
+      <c r="F263" t="n">
+        <v>14337621</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>5759324</v>
+      </c>
+      <c r="B264" t="n">
+        <v>14475893</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>5759324</v>
+      </c>
+      <c r="F264" t="n">
+        <v>14475893</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>5794260</v>
+      </c>
+      <c r="B265" t="n">
+        <v>14615161</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>5794260</v>
+      </c>
+      <c r="F265" t="n">
+        <v>14615161</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>5830943</v>
+      </c>
+      <c r="B266" t="n">
+        <v>14757180</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>5830943</v>
+      </c>
+      <c r="F266" t="n">
+        <v>14757180</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>5867626</v>
+      </c>
+      <c r="B267" t="n">
+        <v>14900223</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>5867626</v>
+      </c>
+      <c r="F267" t="n">
+        <v>14900223</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>5904309</v>
+      </c>
+      <c r="B268" t="n">
+        <v>15044297</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>5904309</v>
+      </c>
+      <c r="F268" t="n">
+        <v>15044297</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>5940992</v>
+      </c>
+      <c r="B269" t="n">
+        <v>15189409</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>5940992</v>
+      </c>
+      <c r="F269" t="n">
+        <v>15189409</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>5977675</v>
+      </c>
+      <c r="B270" t="n">
+        <v>15335567</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>5977675</v>
+      </c>
+      <c r="F270" t="n">
+        <v>15335567</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>6014358</v>
+      </c>
+      <c r="B271" t="n">
+        <v>15482778</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>6014358</v>
+      </c>
+      <c r="F271" t="n">
+        <v>15482778</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>6051041</v>
+      </c>
+      <c r="B272" t="n">
+        <v>15631050</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>6051041</v>
+      </c>
+      <c r="F272" t="n">
+        <v>15631050</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>6087724</v>
+      </c>
+      <c r="B273" t="n">
+        <v>15780391</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>6087724</v>
+      </c>
+      <c r="F273" t="n">
+        <v>15780391</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>6124407</v>
+      </c>
+      <c r="B274" t="n">
+        <v>15930808</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>6124407</v>
+      </c>
+      <c r="F274" t="n">
+        <v>15930808</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>6161090</v>
+      </c>
+      <c r="B275" t="n">
+        <v>16082309</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>6161090</v>
+      </c>
+      <c r="F275" t="n">
+        <v>16082309</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>6197773</v>
+      </c>
+      <c r="B276" t="n">
+        <v>16234902</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>6197773</v>
+      </c>
+      <c r="F276" t="n">
+        <v>16234902</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>6234456</v>
+      </c>
+      <c r="B277" t="n">
+        <v>16388595</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>6234456</v>
+      </c>
+      <c r="F277" t="n">
+        <v>16388595</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>6272973</v>
+      </c>
+      <c r="B278" t="n">
+        <v>16545230</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>6272973</v>
+      </c>
+      <c r="F278" t="n">
+        <v>16545230</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>6311490</v>
+      </c>
+      <c r="B279" t="n">
+        <v>16702994</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>6311490</v>
+      </c>
+      <c r="F279" t="n">
+        <v>16702994</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>6350007</v>
+      </c>
+      <c r="B280" t="n">
+        <v>16861895</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>6350007</v>
+      </c>
+      <c r="F280" t="n">
+        <v>16861895</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>6388524</v>
+      </c>
+      <c r="B281" t="n">
+        <v>17021941</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>6388524</v>
+      </c>
+      <c r="F281" t="n">
+        <v>17021941</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>6427041</v>
+      </c>
+      <c r="B282" t="n">
+        <v>17183141</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>6427041</v>
+      </c>
+      <c r="F282" t="n">
+        <v>17183141</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>6465558</v>
+      </c>
+      <c r="B283" t="n">
+        <v>17345502</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>6465558</v>
+      </c>
+      <c r="F283" t="n">
+        <v>17345502</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>6504075</v>
+      </c>
+      <c r="B284" t="n">
+        <v>17509034</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>6504075</v>
+      </c>
+      <c r="F284" t="n">
+        <v>17509034</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>6542592</v>
+      </c>
+      <c r="B285" t="n">
+        <v>17673744</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>6542592</v>
+      </c>
+      <c r="F285" t="n">
+        <v>17673744</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>6581109</v>
+      </c>
+      <c r="B286" t="n">
+        <v>17839641</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>6581109</v>
+      </c>
+      <c r="F286" t="n">
+        <v>17839641</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>6619626</v>
+      </c>
+      <c r="B287" t="n">
+        <v>18006734</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>6619626</v>
+      </c>
+      <c r="F287" t="n">
+        <v>18006734</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>6658143</v>
+      </c>
+      <c r="B288" t="n">
+        <v>18175031</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>6658143</v>
+      </c>
+      <c r="F288" t="n">
+        <v>18175031</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>6696660</v>
+      </c>
+      <c r="B289" t="n">
+        <v>18344541</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>6696660</v>
+      </c>
+      <c r="F289" t="n">
+        <v>18344541</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>6737103</v>
+      </c>
+      <c r="B290" t="n">
+        <v>18517199</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>6737103</v>
+      </c>
+      <c r="F290" t="n">
+        <v>18517199</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>6777546</v>
+      </c>
+      <c r="B291" t="n">
+        <v>18691101</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>6777546</v>
+      </c>
+      <c r="F291" t="n">
+        <v>18691101</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>6817989</v>
+      </c>
+      <c r="B292" t="n">
+        <v>18866257</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>6817989</v>
+      </c>
+      <c r="F292" t="n">
+        <v>18866257</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>6858432</v>
+      </c>
+      <c r="B293" t="n">
+        <v>19042675</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>6858432</v>
+      </c>
+      <c r="F293" t="n">
+        <v>19042675</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>6898875</v>
+      </c>
+      <c r="B294" t="n">
+        <v>19220365</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>6898875</v>
+      </c>
+      <c r="F294" t="n">
+        <v>19220365</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>6939318</v>
+      </c>
+      <c r="B295" t="n">
+        <v>19399335</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>6939318</v>
+      </c>
+      <c r="F295" t="n">
+        <v>19399335</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>6979761</v>
+      </c>
+      <c r="B296" t="n">
+        <v>19579595</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>6979761</v>
+      </c>
+      <c r="F296" t="n">
+        <v>19579595</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>7020204</v>
+      </c>
+      <c r="B297" t="n">
+        <v>19761154</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>7020204</v>
+      </c>
+      <c r="F297" t="n">
+        <v>19761154</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>7060647</v>
+      </c>
+      <c r="B298" t="n">
+        <v>19944022</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>7060647</v>
+      </c>
+      <c r="F298" t="n">
+        <v>19944022</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>7101090</v>
+      </c>
+      <c r="B299" t="n">
+        <v>20128208</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>7101090</v>
+      </c>
+      <c r="F299" t="n">
+        <v>20128208</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>7141533</v>
+      </c>
+      <c r="B300" t="n">
+        <v>20313722</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>7141533</v>
+      </c>
+      <c r="F300" t="n">
+        <v>20313722</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>7181976</v>
+      </c>
+      <c r="B301" t="n">
+        <v>20500573</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>7181976</v>
+      </c>
+      <c r="F301" t="n">
+        <v>20500573</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>7224441</v>
+      </c>
+      <c r="B302" t="n">
+        <v>20690792</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>7224441</v>
+      </c>
+      <c r="F302" t="n">
+        <v>20690792</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>7266906</v>
+      </c>
+      <c r="B303" t="n">
+        <v>20882382</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>7266906</v>
+      </c>
+      <c r="F303" t="n">
+        <v>20882382</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>7309371</v>
+      </c>
+      <c r="B304" t="n">
+        <v>21075353</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>7309371</v>
+      </c>
+      <c r="F304" t="n">
+        <v>21075353</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>7351836</v>
+      </c>
+      <c r="B305" t="n">
+        <v>21269715</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>7351836</v>
+      </c>
+      <c r="F305" t="n">
+        <v>21269715</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>7394301</v>
+      </c>
+      <c r="B306" t="n">
+        <v>21465478</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>7394301</v>
+      </c>
+      <c r="F306" t="n">
+        <v>21465478</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>7436766</v>
+      </c>
+      <c r="B307" t="n">
+        <v>21662652</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>7436766</v>
+      </c>
+      <c r="F307" t="n">
+        <v>21662652</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>7479231</v>
+      </c>
+      <c r="B308" t="n">
+        <v>21861247</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>7479231</v>
+      </c>
+      <c r="F308" t="n">
+        <v>21861247</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>7521696</v>
+      </c>
+      <c r="B309" t="n">
+        <v>22061273</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>7521696</v>
+      </c>
+      <c r="F309" t="n">
+        <v>22061273</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>7564161</v>
+      </c>
+      <c r="B310" t="n">
+        <v>22262741</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>7564161</v>
+      </c>
+      <c r="F310" t="n">
+        <v>22262741</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>7606626</v>
+      </c>
+      <c r="B311" t="n">
+        <v>22465661</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>7606626</v>
+      </c>
+      <c r="F311" t="n">
+        <v>22465661</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>7649091</v>
+      </c>
+      <c r="B312" t="n">
+        <v>22670043</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>7649091</v>
+      </c>
+      <c r="F312" t="n">
+        <v>22670043</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>7691556</v>
+      </c>
+      <c r="B313" t="n">
+        <v>22875898</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>7691556</v>
+      </c>
+      <c r="F313" t="n">
+        <v>22875898</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>7736144</v>
+      </c>
+      <c r="B314" t="n">
+        <v>23085360</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>7736144</v>
+      </c>
+      <c r="F314" t="n">
+        <v>23085360</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>7780732</v>
+      </c>
+      <c r="B315" t="n">
+        <v>23296332</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>7780732</v>
+      </c>
+      <c r="F315" t="n">
+        <v>23296332</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>7825320</v>
+      </c>
+      <c r="B316" t="n">
+        <v>23508824</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>7825320</v>
+      </c>
+      <c r="F316" t="n">
+        <v>23508824</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>7869908</v>
+      </c>
+      <c r="B317" t="n">
+        <v>23722848</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>7869908</v>
+      </c>
+      <c r="F317" t="n">
+        <v>23722848</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>7914496</v>
+      </c>
+      <c r="B318" t="n">
+        <v>23938414</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>7914496</v>
+      </c>
+      <c r="F318" t="n">
+        <v>23938414</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>7959084</v>
+      </c>
+      <c r="B319" t="n">
+        <v>24155534</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>7959084</v>
+      </c>
+      <c r="F319" t="n">
+        <v>24155534</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>8003672</v>
+      </c>
+      <c r="B320" t="n">
+        <v>24374219</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>8003672</v>
+      </c>
+      <c r="F320" t="n">
+        <v>24374219</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>8048260</v>
+      </c>
+      <c r="B321" t="n">
+        <v>24594480</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>8048260</v>
+      </c>
+      <c r="F321" t="n">
+        <v>24594480</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>8092848</v>
+      </c>
+      <c r="B322" t="n">
+        <v>24816328</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>8092848</v>
+      </c>
+      <c r="F322" t="n">
+        <v>24816328</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>8137436</v>
+      </c>
+      <c r="B323" t="n">
+        <v>25039775</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>8137436</v>
+      </c>
+      <c r="F323" t="n">
+        <v>25039775</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>8182024</v>
+      </c>
+      <c r="B324" t="n">
+        <v>25264833</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>8182024</v>
+      </c>
+      <c r="F324" t="n">
+        <v>25264833</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>8226612</v>
+      </c>
+      <c r="B325" t="n">
+        <v>25491513</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>8226612</v>
+      </c>
+      <c r="F325" t="n">
+        <v>25491513</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>8273430</v>
+      </c>
+      <c r="B326" t="n">
+        <v>25722057</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>8273430</v>
+      </c>
+      <c r="F326" t="n">
+        <v>25722057</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>8320248</v>
+      </c>
+      <c r="B327" t="n">
+        <v>25954262</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>8320248</v>
+      </c>
+      <c r="F327" t="n">
+        <v>25954262</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>8367066</v>
+      </c>
+      <c r="B328" t="n">
+        <v>26188141</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>8367066</v>
+      </c>
+      <c r="F328" t="n">
+        <v>26188141</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>8413884</v>
+      </c>
+      <c r="B329" t="n">
+        <v>26423705</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>8413884</v>
+      </c>
+      <c r="F329" t="n">
+        <v>26423705</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>8460702</v>
+      </c>
+      <c r="B330" t="n">
+        <v>26660967</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>8460702</v>
+      </c>
+      <c r="F330" t="n">
+        <v>26660967</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>8507520</v>
+      </c>
+      <c r="B331" t="n">
+        <v>26899939</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>8507520</v>
+      </c>
+      <c r="F331" t="n">
+        <v>26899939</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>8554338</v>
+      </c>
+      <c r="B332" t="n">
+        <v>27140634</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>8554338</v>
+      </c>
+      <c r="F332" t="n">
+        <v>27140634</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>8601156</v>
+      </c>
+      <c r="B333" t="n">
+        <v>27383063</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>8601156</v>
+      </c>
+      <c r="F333" t="n">
+        <v>27383063</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>8647974</v>
+      </c>
+      <c r="B334" t="n">
+        <v>27627240</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>8647974</v>
+      </c>
+      <c r="F334" t="n">
+        <v>27627240</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>8694792</v>
+      </c>
+      <c r="B335" t="n">
+        <v>27873176</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>8694792</v>
+      </c>
+      <c r="F335" t="n">
+        <v>27873176</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>8741610</v>
+      </c>
+      <c r="B336" t="n">
+        <v>28120885</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>8741610</v>
+      </c>
+      <c r="F336" t="n">
+        <v>28120885</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>8788428</v>
+      </c>
+      <c r="B337" t="n">
+        <v>28370379</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>8788428</v>
+      </c>
+      <c r="F337" t="n">
+        <v>28370379</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>8837586</v>
+      </c>
+      <c r="B338" t="n">
+        <v>28624011</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>8837586</v>
+      </c>
+      <c r="F338" t="n">
+        <v>28624011</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>8886744</v>
+      </c>
+      <c r="B339" t="n">
+        <v>28879472</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>8886744</v>
+      </c>
+      <c r="F339" t="n">
+        <v>28879472</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>8935902</v>
+      </c>
+      <c r="B340" t="n">
+        <v>29136774</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>8935902</v>
+      </c>
+      <c r="F340" t="n">
+        <v>29136774</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>8985060</v>
+      </c>
+      <c r="B341" t="n">
+        <v>29395930</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>8985060</v>
+      </c>
+      <c r="F341" t="n">
+        <v>29395930</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>9034218</v>
+      </c>
+      <c r="B342" t="n">
+        <v>29656954</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>9034218</v>
+      </c>
+      <c r="F342" t="n">
+        <v>29656954</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>9083376</v>
+      </c>
+      <c r="B343" t="n">
+        <v>29919859</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>9083376</v>
+      </c>
+      <c r="F343" t="n">
+        <v>29919859</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>9132534</v>
+      </c>
+      <c r="B344" t="n">
+        <v>30184659</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>9132534</v>
+      </c>
+      <c r="F344" t="n">
+        <v>30184659</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>9181692</v>
+      </c>
+      <c r="B345" t="n">
+        <v>30451368</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>9181692</v>
+      </c>
+      <c r="F345" t="n">
+        <v>30451368</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>9230850</v>
+      </c>
+      <c r="B346" t="n">
+        <v>30719999</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>9230850</v>
+      </c>
+      <c r="F346" t="n">
+        <v>30719999</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>9280008</v>
+      </c>
+      <c r="B347" t="n">
+        <v>30990566</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>9280008</v>
+      </c>
+      <c r="F347" t="n">
+        <v>30990566</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>9329166</v>
+      </c>
+      <c r="B348" t="n">
+        <v>31263083</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>9329166</v>
+      </c>
+      <c r="F348" t="n">
+        <v>31263083</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>9378324</v>
+      </c>
+      <c r="B349" t="n">
+        <v>31537564</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>9378324</v>
+      </c>
+      <c r="F349" t="n">
+        <v>31537564</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>9429940</v>
+      </c>
+      <c r="B350" t="n">
+        <v>31816481</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>9429940</v>
+      </c>
+      <c r="F350" t="n">
+        <v>31816481</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>9481556</v>
+      </c>
+      <c r="B351" t="n">
+        <v>32097409</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>9481556</v>
+      </c>
+      <c r="F351" t="n">
+        <v>32097409</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>9533172</v>
+      </c>
+      <c r="B352" t="n">
+        <v>32380361</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>9533172</v>
+      </c>
+      <c r="F352" t="n">
+        <v>32380361</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>9584788</v>
+      </c>
+      <c r="B353" t="n">
+        <v>32665353</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>9584788</v>
+      </c>
+      <c r="F353" t="n">
+        <v>32665353</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>9636404</v>
+      </c>
+      <c r="B354" t="n">
+        <v>32952399</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>9636404</v>
+      </c>
+      <c r="F354" t="n">
+        <v>32952399</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>9688020</v>
+      </c>
+      <c r="B355" t="n">
+        <v>33241514</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>9688020</v>
+      </c>
+      <c r="F355" t="n">
+        <v>33241514</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>9739636</v>
+      </c>
+      <c r="B356" t="n">
+        <v>33532712</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>9739636</v>
+      </c>
+      <c r="F356" t="n">
+        <v>33532712</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>9791252</v>
+      </c>
+      <c r="B357" t="n">
+        <v>33826009</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>9791252</v>
+      </c>
+      <c r="F357" t="n">
+        <v>33826009</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>9842868</v>
+      </c>
+      <c r="B358" t="n">
+        <v>34121420</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>9842868</v>
+      </c>
+      <c r="F358" t="n">
+        <v>34121420</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>9894484</v>
+      </c>
+      <c r="B359" t="n">
+        <v>34418960</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>9894484</v>
+      </c>
+      <c r="F359" t="n">
+        <v>34418960</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>9946100</v>
+      </c>
+      <c r="B360" t="n">
+        <v>34718645</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>9946100</v>
+      </c>
+      <c r="F360" t="n">
+        <v>34718645</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>9997716</v>
+      </c>
+      <c r="B361" t="n">
+        <v>35020489</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>9997716</v>
+      </c>
+      <c r="F361" t="n">
+        <v>35020489</v>
       </c>
     </row>
   </sheetData>

--- a/static/investmentSchedule_results.xlsx
+++ b/static/investmentSchedule_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,502 +450,7222 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>12452</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>12452</v>
       </c>
       <c r="C2" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6000000</v>
+        <v>12452</v>
       </c>
       <c r="F2" t="n">
-        <v>6000000</v>
+        <v>12452</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>24904</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>24994</v>
       </c>
       <c r="C3" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>6070289</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6000000</v>
+        <v>24904</v>
       </c>
       <c r="F3" t="n">
-        <v>6070289</v>
+        <v>24994</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>37356</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>37626</v>
       </c>
       <c r="C4" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6141401</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6000000</v>
+        <v>37356</v>
       </c>
       <c r="F4" t="n">
-        <v>6141401</v>
+        <v>37626</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>49808</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>50349</v>
       </c>
       <c r="C5" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>6213347</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6000000</v>
+        <v>49808</v>
       </c>
       <c r="F5" t="n">
-        <v>6213347</v>
+        <v>50349</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>62260</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>63164</v>
       </c>
       <c r="C6" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6286135</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6000000</v>
+        <v>62260</v>
       </c>
       <c r="F6" t="n">
-        <v>6286135</v>
+        <v>63164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>74712</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>76071</v>
       </c>
       <c r="C7" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>6359776</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6000000</v>
+        <v>74712</v>
       </c>
       <c r="F7" t="n">
-        <v>6359776</v>
+        <v>76071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>87164</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>89071</v>
       </c>
       <c r="C8" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6434280</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6000000</v>
+        <v>87164</v>
       </c>
       <c r="F8" t="n">
-        <v>6434280</v>
+        <v>89071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>99616</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>102165</v>
       </c>
       <c r="C9" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6509657</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6000000</v>
+        <v>99616</v>
       </c>
       <c r="F9" t="n">
-        <v>6509657</v>
+        <v>102165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>112068</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>115353</v>
       </c>
       <c r="C10" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>6585917</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6000000</v>
+        <v>112068</v>
       </c>
       <c r="F10" t="n">
-        <v>6585917</v>
+        <v>115353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>124520</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>128636</v>
       </c>
       <c r="C11" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>6663070</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>6000000</v>
+        <v>124520</v>
       </c>
       <c r="F11" t="n">
-        <v>6663070</v>
+        <v>128636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>136972</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>142015</v>
       </c>
       <c r="C12" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>6741127</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>6000000</v>
+        <v>136972</v>
       </c>
       <c r="F12" t="n">
-        <v>6741127</v>
+        <v>142015</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>149424</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>155491</v>
       </c>
       <c r="C13" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>6820098</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6000000</v>
+        <v>149424</v>
       </c>
       <c r="F13" t="n">
-        <v>6820098</v>
+        <v>155491</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>162499</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>169687</v>
       </c>
       <c r="C14" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6899994</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>6000000</v>
+        <v>162499</v>
       </c>
       <c r="F14" t="n">
-        <v>6899994</v>
+        <v>169687</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>175574</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>183985</v>
       </c>
       <c r="C15" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6980826</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>6000000</v>
+        <v>175574</v>
       </c>
       <c r="F15" t="n">
-        <v>6980826</v>
+        <v>183985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>188649</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>198386</v>
       </c>
       <c r="C16" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7062605</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>6000000</v>
+        <v>188649</v>
       </c>
       <c r="F16" t="n">
-        <v>7062605</v>
+        <v>198386</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0</v>
+        <v>201724</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>212891</v>
       </c>
       <c r="C17" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>7145342</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6000000</v>
+        <v>201724</v>
       </c>
       <c r="F17" t="n">
-        <v>7145342</v>
+        <v>212891</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0</v>
+        <v>214799</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>227500</v>
       </c>
       <c r="C18" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7229049</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>6000000</v>
+        <v>214799</v>
       </c>
       <c r="F18" t="n">
-        <v>7229049</v>
+        <v>227500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>227874</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>242215</v>
       </c>
       <c r="C19" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7313736</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6000000</v>
+        <v>227874</v>
       </c>
       <c r="F19" t="n">
-        <v>7313736</v>
+        <v>242215</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0</v>
+        <v>240949</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>257036</v>
       </c>
       <c r="C20" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7399415</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6000000</v>
+        <v>240949</v>
       </c>
       <c r="F20" t="n">
-        <v>7399415</v>
+        <v>257036</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0</v>
+        <v>254024</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>271964</v>
       </c>
       <c r="C21" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7486098</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>6000000</v>
+        <v>254024</v>
       </c>
       <c r="F21" t="n">
-        <v>7486098</v>
+        <v>271964</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0</v>
+        <v>267099</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>286999</v>
       </c>
       <c r="C22" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>7573797</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6000000</v>
+        <v>267099</v>
       </c>
       <c r="F22" t="n">
-        <v>7573797</v>
+        <v>286999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0</v>
+        <v>280174</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>302142</v>
       </c>
       <c r="C23" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>7662523</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>6000000</v>
+        <v>280174</v>
       </c>
       <c r="F23" t="n">
-        <v>7662523</v>
+        <v>302142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0</v>
+        <v>293249</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>317395</v>
       </c>
       <c r="C24" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>7752288</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>6000000</v>
+        <v>293249</v>
       </c>
       <c r="F24" t="n">
-        <v>7752288</v>
+        <v>317395</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0</v>
+        <v>306324</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>332758</v>
       </c>
       <c r="C25" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>7843105</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>6000000</v>
+        <v>306324</v>
       </c>
       <c r="F25" t="n">
-        <v>7843105</v>
+        <v>332758</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0</v>
+        <v>320052</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>348884</v>
       </c>
       <c r="C26" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7934986</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>6000000</v>
+        <v>320052</v>
       </c>
       <c r="F26" t="n">
-        <v>7934986</v>
+        <v>348884</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>333780</v>
+      </c>
+      <c r="B27" t="n">
+        <v>365127</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>333780</v>
+      </c>
+      <c r="F27" t="n">
+        <v>365127</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>347508</v>
+      </c>
+      <c r="B28" t="n">
+        <v>381487</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>347508</v>
+      </c>
+      <c r="F28" t="n">
+        <v>381487</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>361236</v>
+      </c>
+      <c r="B29" t="n">
+        <v>397965</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>361236</v>
+      </c>
+      <c r="F29" t="n">
+        <v>397965</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>374964</v>
+      </c>
+      <c r="B30" t="n">
+        <v>414561</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>374964</v>
+      </c>
+      <c r="F30" t="n">
+        <v>414561</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>388692</v>
+      </c>
+      <c r="B31" t="n">
+        <v>431277</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>388692</v>
+      </c>
+      <c r="F31" t="n">
+        <v>431277</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>402420</v>
+      </c>
+      <c r="B32" t="n">
+        <v>448113</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>402420</v>
+      </c>
+      <c r="F32" t="n">
+        <v>448113</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>416148</v>
+      </c>
+      <c r="B33" t="n">
+        <v>465071</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>416148</v>
+      </c>
+      <c r="F33" t="n">
+        <v>465071</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>429876</v>
+      </c>
+      <c r="B34" t="n">
+        <v>482151</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>429876</v>
+      </c>
+      <c r="F34" t="n">
+        <v>482151</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>443604</v>
+      </c>
+      <c r="B35" t="n">
+        <v>499354</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>443604</v>
+      </c>
+      <c r="F35" t="n">
+        <v>499354</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>457332</v>
+      </c>
+      <c r="B36" t="n">
+        <v>516681</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>457332</v>
+      </c>
+      <c r="F36" t="n">
+        <v>516681</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>471060</v>
+      </c>
+      <c r="B37" t="n">
+        <v>534133</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>471060</v>
+      </c>
+      <c r="F37" t="n">
+        <v>534133</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>485475</v>
+      </c>
+      <c r="B38" t="n">
+        <v>552398</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>485475</v>
+      </c>
+      <c r="F38" t="n">
+        <v>552398</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>499890</v>
+      </c>
+      <c r="B39" t="n">
+        <v>570794</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>499890</v>
+      </c>
+      <c r="F39" t="n">
+        <v>570794</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>514305</v>
+      </c>
+      <c r="B40" t="n">
+        <v>589323</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>514305</v>
+      </c>
+      <c r="F40" t="n">
+        <v>589323</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>528720</v>
+      </c>
+      <c r="B41" t="n">
+        <v>607985</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>528720</v>
+      </c>
+      <c r="F41" t="n">
+        <v>607985</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>543135</v>
+      </c>
+      <c r="B42" t="n">
+        <v>626782</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>543135</v>
+      </c>
+      <c r="F42" t="n">
+        <v>626782</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>557550</v>
+      </c>
+      <c r="B43" t="n">
+        <v>645714</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>557550</v>
+      </c>
+      <c r="F43" t="n">
+        <v>645714</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>571965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>664783</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>571965</v>
+      </c>
+      <c r="F44" t="n">
+        <v>664783</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>586380</v>
+      </c>
+      <c r="B45" t="n">
+        <v>683989</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>586380</v>
+      </c>
+      <c r="F45" t="n">
+        <v>683989</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>600795</v>
+      </c>
+      <c r="B46" t="n">
+        <v>703334</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>600795</v>
+      </c>
+      <c r="F46" t="n">
+        <v>703334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>615210</v>
+      </c>
+      <c r="B47" t="n">
+        <v>722818</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>615210</v>
+      </c>
+      <c r="F47" t="n">
+        <v>722818</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>629625</v>
+      </c>
+      <c r="B48" t="n">
+        <v>742443</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>629625</v>
+      </c>
+      <c r="F48" t="n">
+        <v>742443</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>644040</v>
+      </c>
+      <c r="B49" t="n">
+        <v>762209</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>644040</v>
+      </c>
+      <c r="F49" t="n">
+        <v>762209</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>659175</v>
+      </c>
+      <c r="B50" t="n">
+        <v>782837</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>659175</v>
+      </c>
+      <c r="F50" t="n">
+        <v>782837</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>674310</v>
+      </c>
+      <c r="B51" t="n">
+        <v>803614</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>674310</v>
+      </c>
+      <c r="F51" t="n">
+        <v>803614</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>689445</v>
+      </c>
+      <c r="B52" t="n">
+        <v>824541</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>689445</v>
+      </c>
+      <c r="F52" t="n">
+        <v>824541</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>704580</v>
+      </c>
+      <c r="B53" t="n">
+        <v>845619</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>704580</v>
+      </c>
+      <c r="F53" t="n">
+        <v>845619</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>719715</v>
+      </c>
+      <c r="B54" t="n">
+        <v>866849</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>719715</v>
+      </c>
+      <c r="F54" t="n">
+        <v>866849</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>734850</v>
+      </c>
+      <c r="B55" t="n">
+        <v>888232</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>734850</v>
+      </c>
+      <c r="F55" t="n">
+        <v>888232</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>749985</v>
+      </c>
+      <c r="B56" t="n">
+        <v>909769</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>749985</v>
+      </c>
+      <c r="F56" t="n">
+        <v>909769</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>765120</v>
+      </c>
+      <c r="B57" t="n">
+        <v>931461</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>765120</v>
+      </c>
+      <c r="F57" t="n">
+        <v>931461</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>780255</v>
+      </c>
+      <c r="B58" t="n">
+        <v>953309</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>780255</v>
+      </c>
+      <c r="F58" t="n">
+        <v>953309</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>795390</v>
+      </c>
+      <c r="B59" t="n">
+        <v>975315</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>795390</v>
+      </c>
+      <c r="F59" t="n">
+        <v>975315</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>810525</v>
+      </c>
+      <c r="B60" t="n">
+        <v>997479</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>810525</v>
+      </c>
+      <c r="F60" t="n">
+        <v>997479</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>825660</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1019803</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>825660</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1019803</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>841552</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1043045</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>841552</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1043045</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>857444</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1066455</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>857444</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1066455</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>873336</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1090033</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>873336</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1090033</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>889228</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1113781</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>889228</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1113781</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>905120</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1137700</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>905120</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1137700</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>921012</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1161792</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>921012</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1161792</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>936904</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1186057</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>936904</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1186057</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>952796</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1210497</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>952796</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1210497</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>968688</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1235113</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>968688</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1235113</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>984580</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1259907</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>984580</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1259907</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1000472</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1284880</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1000472</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1284880</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1016364</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1310033</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1016364</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1310033</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1033051</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1336162</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1033051</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1336162</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1049738</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1362479</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1049738</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1362479</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1066425</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1388986</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1066425</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1388986</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1083112</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1415684</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1083112</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1415684</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1099799</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1442574</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1099799</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1442574</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1116486</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1469658</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1116486</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1469658</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1133173</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1496937</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1133173</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1496937</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1149860</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1524413</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1149860</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1524413</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1166547</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1552087</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1166547</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1552087</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1183234</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1579960</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1183234</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1579960</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1199921</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1608034</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1199921</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1608034</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1216608</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1636311</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1216608</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1636311</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1234129</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1665625</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1234129</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1665625</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1251650</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1695151</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1251650</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1695151</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1269171</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1724890</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1269171</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1724890</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1286692</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1754843</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1286692</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1754843</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1304213</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1785012</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1304213</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1785012</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1321734</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1815398</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1321734</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1815398</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1339255</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1846003</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1339255</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1846003</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1356776</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1876829</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1356776</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1876829</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1374297</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1907877</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1374297</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1907877</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1391818</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1939149</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1391818</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1939149</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1409339</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1970646</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1409339</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1970646</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1426860</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2002370</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1426860</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2002370</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1445257</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2035199</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1445257</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2035199</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1463654</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2068264</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1463654</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2068264</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1482051</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2101568</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1482051</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2101568</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1500448</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2135112</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1500448</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2135112</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1518845</v>
+      </c>
+      <c r="B102" t="n">
+        <v>2168897</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1518845</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2168897</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1537242</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2202926</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1537242</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2202926</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1555639</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2237200</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1555639</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2237200</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1574036</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2271721</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1574036</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2271721</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1592433</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2306491</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1592433</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2306491</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1610830</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2341512</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1610830</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2341512</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1629227</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2376785</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1629227</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2376785</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1647624</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2412312</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1647624</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2412312</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>1666941</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2449015</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1666941</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2449015</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>1686258</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2485983</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1686258</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2485983</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>1705575</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2523217</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1705575</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2523217</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>1724892</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2560720</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1724892</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2560720</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>1744209</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2598493</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1744209</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2598493</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>1763526</v>
+      </c>
+      <c r="B115" t="n">
+        <v>2636538</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1763526</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2636538</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>1782843</v>
+      </c>
+      <c r="B116" t="n">
+        <v>2674857</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1782843</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2674857</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>1802160</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2713453</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1802160</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2713453</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>1821477</v>
+      </c>
+      <c r="B118" t="n">
+        <v>2752327</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1821477</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2752327</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>1840794</v>
+      </c>
+      <c r="B119" t="n">
+        <v>2791481</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1840794</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2791481</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>1860111</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2830917</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1860111</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2830917</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>1879428</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2870637</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1879428</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2870637</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>1899711</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2911610</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1899711</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2911610</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>1919994</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2952878</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1919994</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2952878</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>1940277</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2994443</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1940277</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2994443</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>1960560</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3036308</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1960560</v>
+      </c>
+      <c r="F125" t="n">
+        <v>3036308</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>1980843</v>
+      </c>
+      <c r="B126" t="n">
+        <v>3078475</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1980843</v>
+      </c>
+      <c r="F126" t="n">
+        <v>3078475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2001126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>3120946</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2001126</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3120946</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2021409</v>
+      </c>
+      <c r="B128" t="n">
+        <v>3163723</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2021409</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3163723</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2041692</v>
+      </c>
+      <c r="B129" t="n">
+        <v>3206808</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2041692</v>
+      </c>
+      <c r="F129" t="n">
+        <v>3206808</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2061975</v>
+      </c>
+      <c r="B130" t="n">
+        <v>3250204</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2061975</v>
+      </c>
+      <c r="F130" t="n">
+        <v>3250204</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2082258</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3293912</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2082258</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3293912</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2102541</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3337935</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2102541</v>
+      </c>
+      <c r="F132" t="n">
+        <v>3337935</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2122824</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3382276</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2122824</v>
+      </c>
+      <c r="F133" t="n">
+        <v>3382276</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2144121</v>
+      </c>
+      <c r="B134" t="n">
+        <v>3427950</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2144121</v>
+      </c>
+      <c r="F134" t="n">
+        <v>3427950</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2165418</v>
+      </c>
+      <c r="B135" t="n">
+        <v>3473953</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2165418</v>
+      </c>
+      <c r="F135" t="n">
+        <v>3473953</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2186715</v>
+      </c>
+      <c r="B136" t="n">
+        <v>3520288</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2186715</v>
+      </c>
+      <c r="F136" t="n">
+        <v>3520288</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2208012</v>
+      </c>
+      <c r="B137" t="n">
+        <v>3566957</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2208012</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3566957</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2229309</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3613962</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2229309</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3613962</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2250606</v>
+      </c>
+      <c r="B139" t="n">
+        <v>3661306</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2250606</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3661306</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2271903</v>
+      </c>
+      <c r="B140" t="n">
+        <v>3708991</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2271903</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3708991</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2293200</v>
+      </c>
+      <c r="B141" t="n">
+        <v>3757020</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2293200</v>
+      </c>
+      <c r="F141" t="n">
+        <v>3757020</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2314497</v>
+      </c>
+      <c r="B142" t="n">
+        <v>3805395</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2314497</v>
+      </c>
+      <c r="F142" t="n">
+        <v>3805395</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2335794</v>
+      </c>
+      <c r="B143" t="n">
+        <v>3854119</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2335794</v>
+      </c>
+      <c r="F143" t="n">
+        <v>3854119</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2357091</v>
+      </c>
+      <c r="B144" t="n">
+        <v>3903194</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2357091</v>
+      </c>
+      <c r="F144" t="n">
+        <v>3903194</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2378388</v>
+      </c>
+      <c r="B145" t="n">
+        <v>3952623</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2378388</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3952623</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2400750</v>
+      </c>
+      <c r="B146" t="n">
+        <v>4003473</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2400750</v>
+      </c>
+      <c r="F146" t="n">
+        <v>4003473</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2423112</v>
+      </c>
+      <c r="B147" t="n">
+        <v>4054689</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2423112</v>
+      </c>
+      <c r="F147" t="n">
+        <v>4054689</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2445474</v>
+      </c>
+      <c r="B148" t="n">
+        <v>4106274</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2445474</v>
+      </c>
+      <c r="F148" t="n">
+        <v>4106274</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2467836</v>
+      </c>
+      <c r="B149" t="n">
+        <v>4158231</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2467836</v>
+      </c>
+      <c r="F149" t="n">
+        <v>4158231</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2490198</v>
+      </c>
+      <c r="B150" t="n">
+        <v>4210563</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2490198</v>
+      </c>
+      <c r="F150" t="n">
+        <v>4210563</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2512560</v>
+      </c>
+      <c r="B151" t="n">
+        <v>4263272</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2512560</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4263272</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2534922</v>
+      </c>
+      <c r="B152" t="n">
+        <v>4316361</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2534922</v>
+      </c>
+      <c r="F152" t="n">
+        <v>4316361</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2557284</v>
+      </c>
+      <c r="B153" t="n">
+        <v>4369832</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2557284</v>
+      </c>
+      <c r="F153" t="n">
+        <v>4369832</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2579646</v>
+      </c>
+      <c r="B154" t="n">
+        <v>4423689</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2579646</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4423689</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2602008</v>
+      </c>
+      <c r="B155" t="n">
+        <v>4477934</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2602008</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4477934</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2624370</v>
+      </c>
+      <c r="B156" t="n">
+        <v>4532570</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2624370</v>
+      </c>
+      <c r="F156" t="n">
+        <v>4532570</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2646732</v>
+      </c>
+      <c r="B157" t="n">
+        <v>4587600</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2646732</v>
+      </c>
+      <c r="F157" t="n">
+        <v>4587600</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2670212</v>
+      </c>
+      <c r="B158" t="n">
+        <v>4644144</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>2670212</v>
+      </c>
+      <c r="F158" t="n">
+        <v>4644144</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2693692</v>
+      </c>
+      <c r="B159" t="n">
+        <v>4701096</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>2693692</v>
+      </c>
+      <c r="F159" t="n">
+        <v>4701096</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2717172</v>
+      </c>
+      <c r="B160" t="n">
+        <v>4758458</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>2717172</v>
+      </c>
+      <c r="F160" t="n">
+        <v>4758458</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2740652</v>
+      </c>
+      <c r="B161" t="n">
+        <v>4816234</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2740652</v>
+      </c>
+      <c r="F161" t="n">
+        <v>4816234</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2764132</v>
+      </c>
+      <c r="B162" t="n">
+        <v>4874426</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2764132</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4874426</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2787612</v>
+      </c>
+      <c r="B163" t="n">
+        <v>4933038</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2787612</v>
+      </c>
+      <c r="F163" t="n">
+        <v>4933038</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2811092</v>
+      </c>
+      <c r="B164" t="n">
+        <v>4992072</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2811092</v>
+      </c>
+      <c r="F164" t="n">
+        <v>4992072</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2834572</v>
+      </c>
+      <c r="B165" t="n">
+        <v>5051531</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2834572</v>
+      </c>
+      <c r="F165" t="n">
+        <v>5051531</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2858052</v>
+      </c>
+      <c r="B166" t="n">
+        <v>5111419</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2858052</v>
+      </c>
+      <c r="F166" t="n">
+        <v>5111419</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2881532</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5171739</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2881532</v>
+      </c>
+      <c r="F167" t="n">
+        <v>5171739</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2905012</v>
+      </c>
+      <c r="B168" t="n">
+        <v>5232493</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2905012</v>
+      </c>
+      <c r="F168" t="n">
+        <v>5232493</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2928492</v>
+      </c>
+      <c r="B169" t="n">
+        <v>5293685</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2928492</v>
+      </c>
+      <c r="F169" t="n">
+        <v>5293685</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2953146</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5356492</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>2953146</v>
+      </c>
+      <c r="F170" t="n">
+        <v>5356492</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2977800</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5419752</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2977800</v>
+      </c>
+      <c r="F171" t="n">
+        <v>5419752</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>3002454</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5483468</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3002454</v>
+      </c>
+      <c r="F172" t="n">
+        <v>5483468</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>3027108</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5547643</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3027108</v>
+      </c>
+      <c r="F173" t="n">
+        <v>5547643</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>3051762</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5612281</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3051762</v>
+      </c>
+      <c r="F174" t="n">
+        <v>5612281</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>3076416</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5677385</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3076416</v>
+      </c>
+      <c r="F175" t="n">
+        <v>5677385</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>3101070</v>
+      </c>
+      <c r="B176" t="n">
+        <v>5742958</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3101070</v>
+      </c>
+      <c r="F176" t="n">
+        <v>5742958</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>3125724</v>
+      </c>
+      <c r="B177" t="n">
+        <v>5809003</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3125724</v>
+      </c>
+      <c r="F177" t="n">
+        <v>5809003</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>3150378</v>
+      </c>
+      <c r="B178" t="n">
+        <v>5875524</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3150378</v>
+      </c>
+      <c r="F178" t="n">
+        <v>5875524</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>3175032</v>
+      </c>
+      <c r="B179" t="n">
+        <v>5942525</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3175032</v>
+      </c>
+      <c r="F179" t="n">
+        <v>5942525</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>3199686</v>
+      </c>
+      <c r="B180" t="n">
+        <v>6010009</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3199686</v>
+      </c>
+      <c r="F180" t="n">
+        <v>6010009</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>3224340</v>
+      </c>
+      <c r="B181" t="n">
+        <v>6077979</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3224340</v>
+      </c>
+      <c r="F181" t="n">
+        <v>6077979</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>3250227</v>
+      </c>
+      <c r="B182" t="n">
+        <v>6147672</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>3250227</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6147672</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>3276114</v>
+      </c>
+      <c r="B183" t="n">
+        <v>6217867</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3276114</v>
+      </c>
+      <c r="F183" t="n">
+        <v>6217867</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>3302001</v>
+      </c>
+      <c r="B184" t="n">
+        <v>6288568</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3302001</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6288568</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>3327888</v>
+      </c>
+      <c r="B185" t="n">
+        <v>6359779</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>3327888</v>
+      </c>
+      <c r="F185" t="n">
+        <v>6359779</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>3353775</v>
+      </c>
+      <c r="B186" t="n">
+        <v>6431503</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>3353775</v>
+      </c>
+      <c r="F186" t="n">
+        <v>6431503</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>3379662</v>
+      </c>
+      <c r="B187" t="n">
+        <v>6503744</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3379662</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6503744</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>3405549</v>
+      </c>
+      <c r="B188" t="n">
+        <v>6576506</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3405549</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6576506</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>3431436</v>
+      </c>
+      <c r="B189" t="n">
+        <v>6649792</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3431436</v>
+      </c>
+      <c r="F189" t="n">
+        <v>6649792</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>3457323</v>
+      </c>
+      <c r="B190" t="n">
+        <v>6723606</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3457323</v>
+      </c>
+      <c r="F190" t="n">
+        <v>6723606</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>3483210</v>
+      </c>
+      <c r="B191" t="n">
+        <v>6797952</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3483210</v>
+      </c>
+      <c r="F191" t="n">
+        <v>6797952</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>3509097</v>
+      </c>
+      <c r="B192" t="n">
+        <v>6872834</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3509097</v>
+      </c>
+      <c r="F192" t="n">
+        <v>6872834</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>3534984</v>
+      </c>
+      <c r="B193" t="n">
+        <v>6948256</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3534984</v>
+      </c>
+      <c r="F193" t="n">
+        <v>6948256</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>3562165</v>
+      </c>
+      <c r="B194" t="n">
+        <v>7025515</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3562165</v>
+      </c>
+      <c r="F194" t="n">
+        <v>7025515</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>3589346</v>
+      </c>
+      <c r="B195" t="n">
+        <v>7103331</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3589346</v>
+      </c>
+      <c r="F195" t="n">
+        <v>7103331</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>3616527</v>
+      </c>
+      <c r="B196" t="n">
+        <v>7181708</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3616527</v>
+      </c>
+      <c r="F196" t="n">
+        <v>7181708</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>3643708</v>
+      </c>
+      <c r="B197" t="n">
+        <v>7260650</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3643708</v>
+      </c>
+      <c r="F197" t="n">
+        <v>7260650</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>3670889</v>
+      </c>
+      <c r="B198" t="n">
+        <v>7340161</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3670889</v>
+      </c>
+      <c r="F198" t="n">
+        <v>7340161</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>3698070</v>
+      </c>
+      <c r="B199" t="n">
+        <v>7420245</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3698070</v>
+      </c>
+      <c r="F199" t="n">
+        <v>7420245</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>3725251</v>
+      </c>
+      <c r="B200" t="n">
+        <v>7500906</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3725251</v>
+      </c>
+      <c r="F200" t="n">
+        <v>7500906</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>3752432</v>
+      </c>
+      <c r="B201" t="n">
+        <v>7582148</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>3752432</v>
+      </c>
+      <c r="F201" t="n">
+        <v>7582148</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>3779613</v>
+      </c>
+      <c r="B202" t="n">
+        <v>7663976</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>3779613</v>
+      </c>
+      <c r="F202" t="n">
+        <v>7663976</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3806794</v>
+      </c>
+      <c r="B203" t="n">
+        <v>7746394</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3806794</v>
+      </c>
+      <c r="F203" t="n">
+        <v>7746394</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>3833975</v>
+      </c>
+      <c r="B204" t="n">
+        <v>7829406</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3833975</v>
+      </c>
+      <c r="F204" t="n">
+        <v>7829406</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>3861156</v>
+      </c>
+      <c r="B205" t="n">
+        <v>7913016</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3861156</v>
+      </c>
+      <c r="F205" t="n">
+        <v>7913016</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>3889696</v>
+      </c>
+      <c r="B206" t="n">
+        <v>7998588</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3889696</v>
+      </c>
+      <c r="F206" t="n">
+        <v>7998588</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3918236</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8084776</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3918236</v>
+      </c>
+      <c r="F207" t="n">
+        <v>8084776</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3946776</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8171586</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3946776</v>
+      </c>
+      <c r="F208" t="n">
+        <v>8171586</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>3975316</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8259021</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3975316</v>
+      </c>
+      <c r="F209" t="n">
+        <v>8259021</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>4003856</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8347086</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>4003856</v>
+      </c>
+      <c r="F210" t="n">
+        <v>8347086</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>4032396</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8435786</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>4032396</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8435786</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>4060936</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8525125</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>4060936</v>
+      </c>
+      <c r="F212" t="n">
+        <v>8525125</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>4089476</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8615108</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>4089476</v>
+      </c>
+      <c r="F213" t="n">
+        <v>8615108</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>4118016</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8705740</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>4118016</v>
+      </c>
+      <c r="F214" t="n">
+        <v>8705740</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>4146556</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8797025</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>4146556</v>
+      </c>
+      <c r="F215" t="n">
+        <v>8797025</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>4175096</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8888968</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>4175096</v>
+      </c>
+      <c r="F216" t="n">
+        <v>8888968</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>4203636</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8981574</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>4203636</v>
+      </c>
+      <c r="F217" t="n">
+        <v>8981574</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>4233603</v>
+      </c>
+      <c r="B218" t="n">
+        <v>9076274</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>4233603</v>
+      </c>
+      <c r="F218" t="n">
+        <v>9076274</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>4263570</v>
+      </c>
+      <c r="B219" t="n">
+        <v>9171657</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>4263570</v>
+      </c>
+      <c r="F219" t="n">
+        <v>9171657</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>4293537</v>
+      </c>
+      <c r="B220" t="n">
+        <v>9267727</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>4293537</v>
+      </c>
+      <c r="F220" t="n">
+        <v>9267727</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>4323504</v>
+      </c>
+      <c r="B221" t="n">
+        <v>9364490</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>4323504</v>
+      </c>
+      <c r="F221" t="n">
+        <v>9364490</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>4353471</v>
+      </c>
+      <c r="B222" t="n">
+        <v>9461950</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>4353471</v>
+      </c>
+      <c r="F222" t="n">
+        <v>9461950</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>4383438</v>
+      </c>
+      <c r="B223" t="n">
+        <v>9560112</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>4383438</v>
+      </c>
+      <c r="F223" t="n">
+        <v>9560112</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>4413405</v>
+      </c>
+      <c r="B224" t="n">
+        <v>9658982</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>4413405</v>
+      </c>
+      <c r="F224" t="n">
+        <v>9658982</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>4443372</v>
+      </c>
+      <c r="B225" t="n">
+        <v>9758564</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>4443372</v>
+      </c>
+      <c r="F225" t="n">
+        <v>9758564</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>4473339</v>
+      </c>
+      <c r="B226" t="n">
+        <v>9858864</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>4473339</v>
+      </c>
+      <c r="F226" t="n">
+        <v>9858864</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>4503306</v>
+      </c>
+      <c r="B227" t="n">
+        <v>9959887</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>4503306</v>
+      </c>
+      <c r="F227" t="n">
+        <v>9959887</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>4533273</v>
+      </c>
+      <c r="B228" t="n">
+        <v>10061638</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>4533273</v>
+      </c>
+      <c r="F228" t="n">
+        <v>10061638</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>4563240</v>
+      </c>
+      <c r="B229" t="n">
+        <v>10164122</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>4563240</v>
+      </c>
+      <c r="F229" t="n">
+        <v>10164122</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>4594706</v>
+      </c>
+      <c r="B230" t="n">
+        <v>10268844</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>4594706</v>
+      </c>
+      <c r="F230" t="n">
+        <v>10268844</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>4626172</v>
+      </c>
+      <c r="B231" t="n">
+        <v>10374321</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>4626172</v>
+      </c>
+      <c r="F231" t="n">
+        <v>10374321</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>4657638</v>
+      </c>
+      <c r="B232" t="n">
+        <v>10480558</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>4657638</v>
+      </c>
+      <c r="F232" t="n">
+        <v>10480558</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>4689104</v>
+      </c>
+      <c r="B233" t="n">
+        <v>10587561</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>4689104</v>
+      </c>
+      <c r="F233" t="n">
+        <v>10587561</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>4720570</v>
+      </c>
+      <c r="B234" t="n">
+        <v>10695335</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>4720570</v>
+      </c>
+      <c r="F234" t="n">
+        <v>10695335</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>4752036</v>
+      </c>
+      <c r="B235" t="n">
+        <v>10803886</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>4752036</v>
+      </c>
+      <c r="F235" t="n">
+        <v>10803886</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>4783502</v>
+      </c>
+      <c r="B236" t="n">
+        <v>10913219</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>4783502</v>
+      </c>
+      <c r="F236" t="n">
+        <v>10913219</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>4814968</v>
+      </c>
+      <c r="B237" t="n">
+        <v>11023340</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>4814968</v>
+      </c>
+      <c r="F237" t="n">
+        <v>11023340</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>4846434</v>
+      </c>
+      <c r="B238" t="n">
+        <v>11134255</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>4846434</v>
+      </c>
+      <c r="F238" t="n">
+        <v>11134255</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>4877900</v>
+      </c>
+      <c r="B239" t="n">
+        <v>11245969</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>4877900</v>
+      </c>
+      <c r="F239" t="n">
+        <v>11245969</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>4909366</v>
+      </c>
+      <c r="B240" t="n">
+        <v>11358488</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>4909366</v>
+      </c>
+      <c r="F240" t="n">
+        <v>11358488</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>4940832</v>
+      </c>
+      <c r="B241" t="n">
+        <v>11471818</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>4940832</v>
+      </c>
+      <c r="F241" t="n">
+        <v>11471818</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>4973871</v>
+      </c>
+      <c r="B242" t="n">
+        <v>11587538</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>4973871</v>
+      </c>
+      <c r="F242" t="n">
+        <v>11587538</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>5006910</v>
+      </c>
+      <c r="B243" t="n">
+        <v>11704092</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>5006910</v>
+      </c>
+      <c r="F243" t="n">
+        <v>11704092</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>5039949</v>
+      </c>
+      <c r="B244" t="n">
+        <v>11821486</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>5039949</v>
+      </c>
+      <c r="F244" t="n">
+        <v>11821486</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>5072988</v>
+      </c>
+      <c r="B245" t="n">
+        <v>11939726</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>5072988</v>
+      </c>
+      <c r="F245" t="n">
+        <v>11939726</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>5106027</v>
+      </c>
+      <c r="B246" t="n">
+        <v>12058818</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>5106027</v>
+      </c>
+      <c r="F246" t="n">
+        <v>12058818</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>5139066</v>
+      </c>
+      <c r="B247" t="n">
+        <v>12178769</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>5139066</v>
+      </c>
+      <c r="F247" t="n">
+        <v>12178769</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>5172105</v>
+      </c>
+      <c r="B248" t="n">
+        <v>12299584</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>5172105</v>
+      </c>
+      <c r="F248" t="n">
+        <v>12299584</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>5205144</v>
+      </c>
+      <c r="B249" t="n">
+        <v>12421270</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>5205144</v>
+      </c>
+      <c r="F249" t="n">
+        <v>12421270</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>5238183</v>
+      </c>
+      <c r="B250" t="n">
+        <v>12543833</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>5238183</v>
+      </c>
+      <c r="F250" t="n">
+        <v>12543833</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>5271222</v>
+      </c>
+      <c r="B251" t="n">
+        <v>12667279</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>5271222</v>
+      </c>
+      <c r="F251" t="n">
+        <v>12667279</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>5304261</v>
+      </c>
+      <c r="B252" t="n">
+        <v>12791615</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>5304261</v>
+      </c>
+      <c r="F252" t="n">
+        <v>12791615</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>5337300</v>
+      </c>
+      <c r="B253" t="n">
+        <v>12916847</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>5337300</v>
+      </c>
+      <c r="F253" t="n">
+        <v>12916847</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>5371991</v>
+      </c>
+      <c r="B254" t="n">
+        <v>13044634</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>5371991</v>
+      </c>
+      <c r="F254" t="n">
+        <v>13044634</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>5406682</v>
+      </c>
+      <c r="B255" t="n">
+        <v>13173342</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>5406682</v>
+      </c>
+      <c r="F255" t="n">
+        <v>13173342</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>5441373</v>
+      </c>
+      <c r="B256" t="n">
+        <v>13302978</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>5441373</v>
+      </c>
+      <c r="F256" t="n">
+        <v>13302978</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>5476064</v>
+      </c>
+      <c r="B257" t="n">
+        <v>13433548</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>5476064</v>
+      </c>
+      <c r="F257" t="n">
+        <v>13433548</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>5510755</v>
+      </c>
+      <c r="B258" t="n">
+        <v>13565059</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>5510755</v>
+      </c>
+      <c r="F258" t="n">
+        <v>13565059</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>5545446</v>
+      </c>
+      <c r="B259" t="n">
+        <v>13697518</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>5545446</v>
+      </c>
+      <c r="F259" t="n">
+        <v>13697518</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>5580137</v>
+      </c>
+      <c r="B260" t="n">
+        <v>13830931</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>5580137</v>
+      </c>
+      <c r="F260" t="n">
+        <v>13830931</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>5614828</v>
+      </c>
+      <c r="B261" t="n">
+        <v>13965306</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>5614828</v>
+      </c>
+      <c r="F261" t="n">
+        <v>13965306</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>5649519</v>
+      </c>
+      <c r="B262" t="n">
+        <v>14100649</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>5649519</v>
+      </c>
+      <c r="F262" t="n">
+        <v>14100649</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>5684210</v>
+      </c>
+      <c r="B263" t="n">
+        <v>14236968</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>5684210</v>
+      </c>
+      <c r="F263" t="n">
+        <v>14236968</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>5718901</v>
+      </c>
+      <c r="B264" t="n">
+        <v>14374269</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>5718901</v>
+      </c>
+      <c r="F264" t="n">
+        <v>14374269</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>5753592</v>
+      </c>
+      <c r="B265" t="n">
+        <v>14512560</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>5753592</v>
+      </c>
+      <c r="F265" t="n">
+        <v>14512560</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>5790017</v>
+      </c>
+      <c r="B266" t="n">
+        <v>14653582</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>5790017</v>
+      </c>
+      <c r="F266" t="n">
+        <v>14653582</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>5826442</v>
+      </c>
+      <c r="B267" t="n">
+        <v>14795620</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>5826442</v>
+      </c>
+      <c r="F267" t="n">
+        <v>14795620</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>5862867</v>
+      </c>
+      <c r="B268" t="n">
+        <v>14938682</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>5862867</v>
+      </c>
+      <c r="F268" t="n">
+        <v>14938682</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>5899292</v>
+      </c>
+      <c r="B269" t="n">
+        <v>15082775</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>5899292</v>
+      </c>
+      <c r="F269" t="n">
+        <v>15082775</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>5935717</v>
+      </c>
+      <c r="B270" t="n">
+        <v>15227906</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>5935717</v>
+      </c>
+      <c r="F270" t="n">
+        <v>15227906</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>5972142</v>
+      </c>
+      <c r="B271" t="n">
+        <v>15374083</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>5972142</v>
+      </c>
+      <c r="F271" t="n">
+        <v>15374083</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>6008567</v>
+      </c>
+      <c r="B272" t="n">
+        <v>15521314</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>6008567</v>
+      </c>
+      <c r="F272" t="n">
+        <v>15521314</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>6044992</v>
+      </c>
+      <c r="B273" t="n">
+        <v>15669606</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>6044992</v>
+      </c>
+      <c r="F273" t="n">
+        <v>15669606</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>6081417</v>
+      </c>
+      <c r="B274" t="n">
+        <v>15818967</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>6081417</v>
+      </c>
+      <c r="F274" t="n">
+        <v>15818967</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>6117842</v>
+      </c>
+      <c r="B275" t="n">
+        <v>15969404</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>6117842</v>
+      </c>
+      <c r="F275" t="n">
+        <v>15969404</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>6154267</v>
+      </c>
+      <c r="B276" t="n">
+        <v>16120926</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>6154267</v>
+      </c>
+      <c r="F276" t="n">
+        <v>16120926</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>6190692</v>
+      </c>
+      <c r="B277" t="n">
+        <v>16273540</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>6190692</v>
+      </c>
+      <c r="F277" t="n">
+        <v>16273540</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>6228939</v>
+      </c>
+      <c r="B278" t="n">
+        <v>16429076</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>6228939</v>
+      </c>
+      <c r="F278" t="n">
+        <v>16429076</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>6267186</v>
+      </c>
+      <c r="B279" t="n">
+        <v>16585733</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>6267186</v>
+      </c>
+      <c r="F279" t="n">
+        <v>16585733</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>6305433</v>
+      </c>
+      <c r="B280" t="n">
+        <v>16743519</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>6305433</v>
+      </c>
+      <c r="F280" t="n">
+        <v>16743519</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>6343680</v>
+      </c>
+      <c r="B281" t="n">
+        <v>16902442</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>6343680</v>
+      </c>
+      <c r="F281" t="n">
+        <v>16902442</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>6381927</v>
+      </c>
+      <c r="B282" t="n">
+        <v>17062510</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>6381927</v>
+      </c>
+      <c r="F282" t="n">
+        <v>17062510</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>6420174</v>
+      </c>
+      <c r="B283" t="n">
+        <v>17223732</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>6420174</v>
+      </c>
+      <c r="F283" t="n">
+        <v>17223732</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>6458421</v>
+      </c>
+      <c r="B284" t="n">
+        <v>17386116</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>6458421</v>
+      </c>
+      <c r="F284" t="n">
+        <v>17386116</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>6496668</v>
+      </c>
+      <c r="B285" t="n">
+        <v>17549670</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>6496668</v>
+      </c>
+      <c r="F285" t="n">
+        <v>17549670</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>6534915</v>
+      </c>
+      <c r="B286" t="n">
+        <v>17714403</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>6534915</v>
+      </c>
+      <c r="F286" t="n">
+        <v>17714403</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>6573162</v>
+      </c>
+      <c r="B287" t="n">
+        <v>17880323</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>6573162</v>
+      </c>
+      <c r="F287" t="n">
+        <v>17880323</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>6611409</v>
+      </c>
+      <c r="B288" t="n">
+        <v>18047439</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>6611409</v>
+      </c>
+      <c r="F288" t="n">
+        <v>18047439</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>6649656</v>
+      </c>
+      <c r="B289" t="n">
+        <v>18215760</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>6649656</v>
+      </c>
+      <c r="F289" t="n">
+        <v>18215760</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>6689815</v>
+      </c>
+      <c r="B290" t="n">
+        <v>18387206</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>6689815</v>
+      </c>
+      <c r="F290" t="n">
+        <v>18387206</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>6729974</v>
+      </c>
+      <c r="B291" t="n">
+        <v>18559888</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>6729974</v>
+      </c>
+      <c r="F291" t="n">
+        <v>18559888</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>6770133</v>
+      </c>
+      <c r="B292" t="n">
+        <v>18733814</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>6770133</v>
+      </c>
+      <c r="F292" t="n">
+        <v>18733814</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>6810292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>18908994</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>6810292</v>
+      </c>
+      <c r="F293" t="n">
+        <v>18908994</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>6850451</v>
+      </c>
+      <c r="B294" t="n">
+        <v>19085436</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>6850451</v>
+      </c>
+      <c r="F294" t="n">
+        <v>19085436</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>6890610</v>
+      </c>
+      <c r="B295" t="n">
+        <v>19263150</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>6890610</v>
+      </c>
+      <c r="F295" t="n">
+        <v>19263150</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>6930769</v>
+      </c>
+      <c r="B296" t="n">
+        <v>19442145</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>6930769</v>
+      </c>
+      <c r="F296" t="n">
+        <v>19442145</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>6970928</v>
+      </c>
+      <c r="B297" t="n">
+        <v>19622430</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>6970928</v>
+      </c>
+      <c r="F297" t="n">
+        <v>19622430</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>7011087</v>
+      </c>
+      <c r="B298" t="n">
+        <v>19804014</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>7011087</v>
+      </c>
+      <c r="F298" t="n">
+        <v>19804014</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>7051246</v>
+      </c>
+      <c r="B299" t="n">
+        <v>19986907</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>7051246</v>
+      </c>
+      <c r="F299" t="n">
+        <v>19986907</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>7091405</v>
+      </c>
+      <c r="B300" t="n">
+        <v>20171118</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>7091405</v>
+      </c>
+      <c r="F300" t="n">
+        <v>20171118</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>7131564</v>
+      </c>
+      <c r="B301" t="n">
+        <v>20356657</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>7131564</v>
+      </c>
+      <c r="F301" t="n">
+        <v>20356657</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>7173731</v>
+      </c>
+      <c r="B302" t="n">
+        <v>20545541</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>7173731</v>
+      </c>
+      <c r="F302" t="n">
+        <v>20545541</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>7215898</v>
+      </c>
+      <c r="B303" t="n">
+        <v>20735786</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>7215898</v>
+      </c>
+      <c r="F303" t="n">
+        <v>20735786</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>7258065</v>
+      </c>
+      <c r="B304" t="n">
+        <v>20927403</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>7258065</v>
+      </c>
+      <c r="F304" t="n">
+        <v>20927403</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>7300232</v>
+      </c>
+      <c r="B305" t="n">
+        <v>21120401</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>7300232</v>
+      </c>
+      <c r="F305" t="n">
+        <v>21120401</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>7342399</v>
+      </c>
+      <c r="B306" t="n">
+        <v>21314790</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>7342399</v>
+      </c>
+      <c r="F306" t="n">
+        <v>21314790</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>7384566</v>
+      </c>
+      <c r="B307" t="n">
+        <v>21510580</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>7384566</v>
+      </c>
+      <c r="F307" t="n">
+        <v>21510580</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>7426733</v>
+      </c>
+      <c r="B308" t="n">
+        <v>21707781</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>7426733</v>
+      </c>
+      <c r="F308" t="n">
+        <v>21707781</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>7468900</v>
+      </c>
+      <c r="B309" t="n">
+        <v>21906403</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>7468900</v>
+      </c>
+      <c r="F309" t="n">
+        <v>21906403</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>7511067</v>
+      </c>
+      <c r="B310" t="n">
+        <v>22106457</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>7511067</v>
+      </c>
+      <c r="F310" t="n">
+        <v>22106457</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>7553234</v>
+      </c>
+      <c r="B311" t="n">
+        <v>22307952</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>7553234</v>
+      </c>
+      <c r="F311" t="n">
+        <v>22307952</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>7595401</v>
+      </c>
+      <c r="B312" t="n">
+        <v>22510900</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>7595401</v>
+      </c>
+      <c r="F312" t="n">
+        <v>22510900</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>7637568</v>
+      </c>
+      <c r="B313" t="n">
+        <v>22715310</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>7637568</v>
+      </c>
+      <c r="F313" t="n">
+        <v>22715310</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>7681843</v>
+      </c>
+      <c r="B314" t="n">
+        <v>22923302</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>7681843</v>
+      </c>
+      <c r="F314" t="n">
+        <v>22923302</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>7726118</v>
+      </c>
+      <c r="B315" t="n">
+        <v>23132793</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>7726118</v>
+      </c>
+      <c r="F315" t="n">
+        <v>23132793</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>7770393</v>
+      </c>
+      <c r="B316" t="n">
+        <v>23343794</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>7770393</v>
+      </c>
+      <c r="F316" t="n">
+        <v>23343794</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>7814668</v>
+      </c>
+      <c r="B317" t="n">
+        <v>23556315</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>7814668</v>
+      </c>
+      <c r="F317" t="n">
+        <v>23556315</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>7858943</v>
+      </c>
+      <c r="B318" t="n">
+        <v>23770368</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>7858943</v>
+      </c>
+      <c r="F318" t="n">
+        <v>23770368</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>7903218</v>
+      </c>
+      <c r="B319" t="n">
+        <v>23985964</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>7903218</v>
+      </c>
+      <c r="F319" t="n">
+        <v>23985964</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>7947493</v>
+      </c>
+      <c r="B320" t="n">
+        <v>24203114</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>7947493</v>
+      </c>
+      <c r="F320" t="n">
+        <v>24203114</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>7991768</v>
+      </c>
+      <c r="B321" t="n">
+        <v>24421829</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>7991768</v>
+      </c>
+      <c r="F321" t="n">
+        <v>24421829</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>8036043</v>
+      </c>
+      <c r="B322" t="n">
+        <v>24642120</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>8036043</v>
+      </c>
+      <c r="F322" t="n">
+        <v>24642120</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>8080318</v>
+      </c>
+      <c r="B323" t="n">
+        <v>24863999</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>8080318</v>
+      </c>
+      <c r="F323" t="n">
+        <v>24863999</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>8124593</v>
+      </c>
+      <c r="B324" t="n">
+        <v>25087477</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>8124593</v>
+      </c>
+      <c r="F324" t="n">
+        <v>25087477</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>8168868</v>
+      </c>
+      <c r="B325" t="n">
+        <v>25312566</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>8168868</v>
+      </c>
+      <c r="F325" t="n">
+        <v>25312566</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>8215357</v>
+      </c>
+      <c r="B326" t="n">
+        <v>25541491</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>8215357</v>
+      </c>
+      <c r="F326" t="n">
+        <v>25541491</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>8261846</v>
+      </c>
+      <c r="B327" t="n">
+        <v>25772066</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>8261846</v>
+      </c>
+      <c r="F327" t="n">
+        <v>25772066</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>8308335</v>
+      </c>
+      <c r="B328" t="n">
+        <v>26004303</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>8308335</v>
+      </c>
+      <c r="F328" t="n">
+        <v>26004303</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>8354824</v>
+      </c>
+      <c r="B329" t="n">
+        <v>26238213</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>8354824</v>
+      </c>
+      <c r="F329" t="n">
+        <v>26238213</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>8401313</v>
+      </c>
+      <c r="B330" t="n">
+        <v>26473809</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>8401313</v>
+      </c>
+      <c r="F330" t="n">
+        <v>26473809</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>8447802</v>
+      </c>
+      <c r="B331" t="n">
+        <v>26711103</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>8447802</v>
+      </c>
+      <c r="F331" t="n">
+        <v>26711103</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>8494291</v>
+      </c>
+      <c r="B332" t="n">
+        <v>26950108</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>8494291</v>
+      </c>
+      <c r="F332" t="n">
+        <v>26950108</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>8540780</v>
+      </c>
+      <c r="B333" t="n">
+        <v>27190835</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>8540780</v>
+      </c>
+      <c r="F333" t="n">
+        <v>27190835</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>8587269</v>
+      </c>
+      <c r="B334" t="n">
+        <v>27433297</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>8587269</v>
+      </c>
+      <c r="F334" t="n">
+        <v>27433297</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>8633758</v>
+      </c>
+      <c r="B335" t="n">
+        <v>27677507</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>8633758</v>
+      </c>
+      <c r="F335" t="n">
+        <v>27677507</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>8680247</v>
+      </c>
+      <c r="B336" t="n">
+        <v>27923477</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>8680247</v>
+      </c>
+      <c r="F336" t="n">
+        <v>27923477</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>8726736</v>
+      </c>
+      <c r="B337" t="n">
+        <v>28171220</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>8726736</v>
+      </c>
+      <c r="F337" t="n">
+        <v>28171220</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>8775549</v>
+      </c>
+      <c r="B338" t="n">
+        <v>28423072</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>8775549</v>
+      </c>
+      <c r="F338" t="n">
+        <v>28423072</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>8824362</v>
+      </c>
+      <c r="B339" t="n">
+        <v>28676739</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>8824362</v>
+      </c>
+      <c r="F339" t="n">
+        <v>28676739</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>8873175</v>
+      </c>
+      <c r="B340" t="n">
+        <v>28932235</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>8873175</v>
+      </c>
+      <c r="F340" t="n">
+        <v>28932235</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>8921988</v>
+      </c>
+      <c r="B341" t="n">
+        <v>29189572</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>8921988</v>
+      </c>
+      <c r="F341" t="n">
+        <v>29189572</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>8970801</v>
+      </c>
+      <c r="B342" t="n">
+        <v>29448764</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>8970801</v>
+      </c>
+      <c r="F342" t="n">
+        <v>29448764</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>9019614</v>
+      </c>
+      <c r="B343" t="n">
+        <v>29709824</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>9019614</v>
+      </c>
+      <c r="F343" t="n">
+        <v>29709824</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>9068427</v>
+      </c>
+      <c r="B344" t="n">
+        <v>29972765</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>9068427</v>
+      </c>
+      <c r="F344" t="n">
+        <v>29972765</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>9117240</v>
+      </c>
+      <c r="B345" t="n">
+        <v>30237601</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>9117240</v>
+      </c>
+      <c r="F345" t="n">
+        <v>30237601</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>9166053</v>
+      </c>
+      <c r="B346" t="n">
+        <v>30504346</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>9166053</v>
+      </c>
+      <c r="F346" t="n">
+        <v>30504346</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>9214866</v>
+      </c>
+      <c r="B347" t="n">
+        <v>30773014</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>9214866</v>
+      </c>
+      <c r="F347" t="n">
+        <v>30773014</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>9263679</v>
+      </c>
+      <c r="B348" t="n">
+        <v>31043618</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>9263679</v>
+      </c>
+      <c r="F348" t="n">
+        <v>31043618</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>9312492</v>
+      </c>
+      <c r="B349" t="n">
+        <v>31316172</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>9312492</v>
+      </c>
+      <c r="F349" t="n">
+        <v>31316172</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>9363746</v>
+      </c>
+      <c r="B350" t="n">
+        <v>31593132</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>9363746</v>
+      </c>
+      <c r="F350" t="n">
+        <v>31593132</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>9415000</v>
+      </c>
+      <c r="B351" t="n">
+        <v>31872088</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>9415000</v>
+      </c>
+      <c r="F351" t="n">
+        <v>31872088</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>9466254</v>
+      </c>
+      <c r="B352" t="n">
+        <v>32153054</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>9466254</v>
+      </c>
+      <c r="F352" t="n">
+        <v>32153054</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>9517508</v>
+      </c>
+      <c r="B353" t="n">
+        <v>32436045</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>9517508</v>
+      </c>
+      <c r="F353" t="n">
+        <v>32436045</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>9568762</v>
+      </c>
+      <c r="B354" t="n">
+        <v>32721076</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>9568762</v>
+      </c>
+      <c r="F354" t="n">
+        <v>32721076</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>9620016</v>
+      </c>
+      <c r="B355" t="n">
+        <v>33008161</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>9620016</v>
+      </c>
+      <c r="F355" t="n">
+        <v>33008161</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>9671270</v>
+      </c>
+      <c r="B356" t="n">
+        <v>33297315</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>9671270</v>
+      </c>
+      <c r="F356" t="n">
+        <v>33297315</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>9722524</v>
+      </c>
+      <c r="B357" t="n">
+        <v>33588554</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>9722524</v>
+      </c>
+      <c r="F357" t="n">
+        <v>33588554</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>9773778</v>
+      </c>
+      <c r="B358" t="n">
+        <v>33881892</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>9773778</v>
+      </c>
+      <c r="F358" t="n">
+        <v>33881892</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>9825032</v>
+      </c>
+      <c r="B359" t="n">
+        <v>34177344</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>9825032</v>
+      </c>
+      <c r="F359" t="n">
+        <v>34177344</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>9876286</v>
+      </c>
+      <c r="B360" t="n">
+        <v>34474925</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>9876286</v>
+      </c>
+      <c r="F360" t="n">
+        <v>34474925</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>9927540</v>
+      </c>
+      <c r="B361" t="n">
+        <v>34774651</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>9927540</v>
+      </c>
+      <c r="F361" t="n">
+        <v>34774651</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>9927540</v>
+      </c>
+      <c r="B362" t="n">
+        <v>35025283</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>9927540</v>
+      </c>
+      <c r="F362" t="n">
+        <v>35025283</v>
       </c>
     </row>
   </sheetData>
